--- a/filer/37118311_vestfyn.xlsx
+++ b/filer/37118311_vestfyn.xlsx
@@ -615,7 +615,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.kr.)</t>
+          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.kr.) · Klasse C-mellem · Revision</t>
         </is>
       </c>
     </row>

--- a/filer/37118311_vestfyn.xlsx
+++ b/filer/37118311_vestfyn.xlsx
@@ -595,7 +595,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L97"/>
+  <dimension ref="A1:L95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -629,7 +629,7 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Indekstal (2020=100)</t>
+          <t>Indekstal (2021=100)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -644,35 +644,35 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
@@ -1402,41 +1402,41 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="21" ht="16" customHeight="1">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>Udviklingsprojekter</t>
+          <t>Grunde og bygninger</t>
         </is>
       </c>
       <c r="B21" s="11">
@@ -1484,7 +1484,7 @@
     <row r="22" ht="16" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>Patenter, varemærker mv.</t>
+          <t>Produktionsanlæg og maskiner</t>
         </is>
       </c>
       <c r="B22" s="5">
@@ -1532,7 +1532,7 @@
     <row r="23" ht="16" customHeight="1">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>Goodwill</t>
+          <t>Driftsmateriel og inventar</t>
         </is>
       </c>
       <c r="B23" s="11">
@@ -1578,49 +1578,49 @@
       </c>
     </row>
     <row r="24" ht="16" customHeight="1">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>Immaterielle anlægsaktiver</t>
-        </is>
-      </c>
-      <c r="B24" s="8">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Indretning af lejede lokaler</t>
+        </is>
+      </c>
+      <c r="B24" s="5">
         <f>'balance_raw_37118311'!$B$5</f>
         <v/>
       </c>
-      <c r="C24" s="8">
+      <c r="C24" s="5">
         <f>'balance_raw_37118311'!$C$5</f>
         <v/>
       </c>
-      <c r="D24" s="8">
+      <c r="D24" s="5">
         <f>'balance_raw_37118311'!$D$5</f>
         <v/>
       </c>
-      <c r="E24" s="8">
+      <c r="E24" s="5">
         <f>'balance_raw_37118311'!$E$5</f>
         <v/>
       </c>
-      <c r="F24" s="8">
+      <c r="F24" s="5">
         <f>'balance_raw_37118311'!$F$5</f>
         <v/>
       </c>
       <c r="G24" t="inlineStr"/>
-      <c r="H24" s="9">
+      <c r="H24" s="6">
         <f>IFERROR(B24/$B$24*100,"")</f>
         <v/>
       </c>
-      <c r="I24" s="9">
+      <c r="I24" s="6">
         <f>IFERROR(C24/$B$24*100,"")</f>
         <v/>
       </c>
-      <c r="J24" s="9">
+      <c r="J24" s="6">
         <f>IFERROR(D24/$B$24*100,"")</f>
         <v/>
       </c>
-      <c r="K24" s="9">
+      <c r="K24" s="6">
         <f>IFERROR(E24/$B$24*100,"")</f>
         <v/>
       </c>
-      <c r="L24" s="9">
+      <c r="L24" s="6">
         <f>IFERROR(F24/$B$24*100,"")</f>
         <v/>
       </c>
@@ -1628,7 +1628,7 @@
     <row r="25" ht="16" customHeight="1">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>Grunde og bygninger</t>
+          <t>Forudbetaling og anlægsaktiver under opførelse</t>
         </is>
       </c>
       <c r="B25" s="11">
@@ -1674,49 +1674,49 @@
       </c>
     </row>
     <row r="26" ht="16" customHeight="1">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>Produktionsanlæg og maskiner</t>
-        </is>
-      </c>
-      <c r="B26" s="5">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>Materielle anlægsaktiver</t>
+        </is>
+      </c>
+      <c r="B26" s="8">
         <f>'balance_raw_37118311'!$B$7</f>
         <v/>
       </c>
-      <c r="C26" s="5">
+      <c r="C26" s="8">
         <f>'balance_raw_37118311'!$C$7</f>
         <v/>
       </c>
-      <c r="D26" s="5">
+      <c r="D26" s="8">
         <f>'balance_raw_37118311'!$D$7</f>
         <v/>
       </c>
-      <c r="E26" s="5">
+      <c r="E26" s="8">
         <f>'balance_raw_37118311'!$E$7</f>
         <v/>
       </c>
-      <c r="F26" s="5">
+      <c r="F26" s="8">
         <f>'balance_raw_37118311'!$F$7</f>
         <v/>
       </c>
       <c r="G26" t="inlineStr"/>
-      <c r="H26" s="6">
+      <c r="H26" s="9">
         <f>IFERROR(B26/$B$26*100,"")</f>
         <v/>
       </c>
-      <c r="I26" s="6">
+      <c r="I26" s="9">
         <f>IFERROR(C26/$B$26*100,"")</f>
         <v/>
       </c>
-      <c r="J26" s="6">
+      <c r="J26" s="9">
         <f>IFERROR(D26/$B$26*100,"")</f>
         <v/>
       </c>
-      <c r="K26" s="6">
+      <c r="K26" s="9">
         <f>IFERROR(E26/$B$26*100,"")</f>
         <v/>
       </c>
-      <c r="L26" s="6">
+      <c r="L26" s="9">
         <f>IFERROR(F26/$B$26*100,"")</f>
         <v/>
       </c>
@@ -1724,7 +1724,7 @@
     <row r="27" ht="16" customHeight="1">
       <c r="A27" s="10" t="inlineStr">
         <is>
-          <t>Driftsmateriel og inventar</t>
+          <t>Kapitalandele, dattervirksomheder</t>
         </is>
       </c>
       <c r="B27" s="11">
@@ -1772,7 +1772,7 @@
     <row r="28" ht="16" customHeight="1">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>Indretning af lejede lokaler</t>
+          <t>Deposita</t>
         </is>
       </c>
       <c r="B28" s="5">
@@ -1818,49 +1818,49 @@
       </c>
     </row>
     <row r="29" ht="16" customHeight="1">
-      <c r="A29" s="10" t="inlineStr">
-        <is>
-          <t>Forudbetaling og anlægsaktiver under opførelse</t>
-        </is>
-      </c>
-      <c r="B29" s="11">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>Finansielle anlægsaktiver</t>
+        </is>
+      </c>
+      <c r="B29" s="8">
         <f>'balance_raw_37118311'!$B$10</f>
         <v/>
       </c>
-      <c r="C29" s="11">
+      <c r="C29" s="8">
         <f>'balance_raw_37118311'!$C$10</f>
         <v/>
       </c>
-      <c r="D29" s="11">
+      <c r="D29" s="8">
         <f>'balance_raw_37118311'!$D$10</f>
         <v/>
       </c>
-      <c r="E29" s="11">
+      <c r="E29" s="8">
         <f>'balance_raw_37118311'!$E$10</f>
         <v/>
       </c>
-      <c r="F29" s="11">
+      <c r="F29" s="8">
         <f>'balance_raw_37118311'!$F$10</f>
         <v/>
       </c>
       <c r="G29" t="inlineStr"/>
-      <c r="H29" s="12">
+      <c r="H29" s="9">
         <f>IFERROR(B29/$B$29*100,"")</f>
         <v/>
       </c>
-      <c r="I29" s="12">
+      <c r="I29" s="9">
         <f>IFERROR(C29/$B$29*100,"")</f>
         <v/>
       </c>
-      <c r="J29" s="12">
+      <c r="J29" s="9">
         <f>IFERROR(D29/$B$29*100,"")</f>
         <v/>
       </c>
-      <c r="K29" s="12">
+      <c r="K29" s="9">
         <f>IFERROR(E29/$B$29*100,"")</f>
         <v/>
       </c>
-      <c r="L29" s="12">
+      <c r="L29" s="9">
         <f>IFERROR(F29/$B$29*100,"")</f>
         <v/>
       </c>
@@ -1868,7 +1868,7 @@
     <row r="30" ht="16" customHeight="1">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>Materielle anlægsaktiver</t>
+          <t>Anlægsaktiver</t>
         </is>
       </c>
       <c r="B30" s="8">
@@ -1916,7 +1916,7 @@
     <row r="31" ht="16" customHeight="1">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t>Kapitalandele, dattervirksomheder</t>
+          <t>Råvarer og hjælpematerialer</t>
         </is>
       </c>
       <c r="B31" s="11">
@@ -1964,7 +1964,7 @@
     <row r="32" ht="16" customHeight="1">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>Deposita</t>
+          <t>Varer under fremstilling</t>
         </is>
       </c>
       <c r="B32" s="5">
@@ -2010,49 +2010,49 @@
       </c>
     </row>
     <row r="33" ht="16" customHeight="1">
-      <c r="A33" s="7" t="inlineStr">
-        <is>
-          <t>Finansielle anlægsaktiver</t>
-        </is>
-      </c>
-      <c r="B33" s="8">
+      <c r="A33" s="10" t="inlineStr">
+        <is>
+          <t>Færdigvarer og handelsvarer</t>
+        </is>
+      </c>
+      <c r="B33" s="11">
         <f>'balance_raw_37118311'!$B$14</f>
         <v/>
       </c>
-      <c r="C33" s="8">
+      <c r="C33" s="11">
         <f>'balance_raw_37118311'!$C$14</f>
         <v/>
       </c>
-      <c r="D33" s="8">
+      <c r="D33" s="11">
         <f>'balance_raw_37118311'!$D$14</f>
         <v/>
       </c>
-      <c r="E33" s="8">
+      <c r="E33" s="11">
         <f>'balance_raw_37118311'!$E$14</f>
         <v/>
       </c>
-      <c r="F33" s="8">
+      <c r="F33" s="11">
         <f>'balance_raw_37118311'!$F$14</f>
         <v/>
       </c>
       <c r="G33" t="inlineStr"/>
-      <c r="H33" s="9">
+      <c r="H33" s="12">
         <f>IFERROR(B33/$B$33*100,"")</f>
         <v/>
       </c>
-      <c r="I33" s="9">
+      <c r="I33" s="12">
         <f>IFERROR(C33/$B$33*100,"")</f>
         <v/>
       </c>
-      <c r="J33" s="9">
+      <c r="J33" s="12">
         <f>IFERROR(D33/$B$33*100,"")</f>
         <v/>
       </c>
-      <c r="K33" s="9">
+      <c r="K33" s="12">
         <f>IFERROR(E33/$B$33*100,"")</f>
         <v/>
       </c>
-      <c r="L33" s="9">
+      <c r="L33" s="12">
         <f>IFERROR(F33/$B$33*100,"")</f>
         <v/>
       </c>
@@ -2060,7 +2060,7 @@
     <row r="34" ht="16" customHeight="1">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>Anlægsaktiver</t>
+          <t>Varebeholdninger</t>
         </is>
       </c>
       <c r="B34" s="8">
@@ -2108,7 +2108,7 @@
     <row r="35" ht="16" customHeight="1">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>Råvarer og hjælpematerialer</t>
+          <t>Tilgodehavender fra salg og tjenesteydelser</t>
         </is>
       </c>
       <c r="B35" s="11">
@@ -2156,7 +2156,7 @@
     <row r="36" ht="16" customHeight="1">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>Varer under fremstilling</t>
+          <t>Tilgodehavender hos tilknyttede virksomheder</t>
         </is>
       </c>
       <c r="B36" s="5">
@@ -2204,7 +2204,7 @@
     <row r="37" ht="16" customHeight="1">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>Færdigvarer og handelsvarer</t>
+          <t>Andre tilgodehavender</t>
         </is>
       </c>
       <c r="B37" s="11">
@@ -2250,49 +2250,49 @@
       </c>
     </row>
     <row r="38" ht="16" customHeight="1">
-      <c r="A38" s="7" t="inlineStr">
-        <is>
-          <t>Varebeholdninger</t>
-        </is>
-      </c>
-      <c r="B38" s="8">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Periodeafgrænsningsposter (aktiver)</t>
+        </is>
+      </c>
+      <c r="B38" s="5">
         <f>'balance_raw_37118311'!$B$19</f>
         <v/>
       </c>
-      <c r="C38" s="8">
+      <c r="C38" s="5">
         <f>'balance_raw_37118311'!$C$19</f>
         <v/>
       </c>
-      <c r="D38" s="8">
+      <c r="D38" s="5">
         <f>'balance_raw_37118311'!$D$19</f>
         <v/>
       </c>
-      <c r="E38" s="8">
+      <c r="E38" s="5">
         <f>'balance_raw_37118311'!$E$19</f>
         <v/>
       </c>
-      <c r="F38" s="8">
+      <c r="F38" s="5">
         <f>'balance_raw_37118311'!$F$19</f>
         <v/>
       </c>
       <c r="G38" t="inlineStr"/>
-      <c r="H38" s="9">
+      <c r="H38" s="6">
         <f>IFERROR(B38/$B$38*100,"")</f>
         <v/>
       </c>
-      <c r="I38" s="9">
+      <c r="I38" s="6">
         <f>IFERROR(C38/$B$38*100,"")</f>
         <v/>
       </c>
-      <c r="J38" s="9">
+      <c r="J38" s="6">
         <f>IFERROR(D38/$B$38*100,"")</f>
         <v/>
       </c>
-      <c r="K38" s="9">
+      <c r="K38" s="6">
         <f>IFERROR(E38/$B$38*100,"")</f>
         <v/>
       </c>
-      <c r="L38" s="9">
+      <c r="L38" s="6">
         <f>IFERROR(F38/$B$38*100,"")</f>
         <v/>
       </c>
@@ -2300,7 +2300,7 @@
     <row r="39" ht="16" customHeight="1">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>Tilgodehavender fra salg og tjenesteydelser</t>
+          <t>Udskudt skatteaktiv</t>
         </is>
       </c>
       <c r="B39" s="11">
@@ -2348,7 +2348,7 @@
     <row r="40" ht="16" customHeight="1">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>Tilgodehavender hos tilknyttede virksomheder</t>
+          <t>Tilgodehavende skat hos tilknyttede virksomheder</t>
         </is>
       </c>
       <c r="B40" s="5">
@@ -2396,7 +2396,7 @@
     <row r="41" ht="16" customHeight="1">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>Andre tilgodehavender</t>
+          <t>Kortfristede skattetilgodehavender</t>
         </is>
       </c>
       <c r="B41" s="11">
@@ -2442,49 +2442,49 @@
       </c>
     </row>
     <row r="42" ht="16" customHeight="1">
-      <c r="A42" s="4" t="inlineStr">
-        <is>
-          <t>Periodeafgrænsningsposter (aktiver)</t>
-        </is>
-      </c>
-      <c r="B42" s="5">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>Tilgodehavender</t>
+        </is>
+      </c>
+      <c r="B42" s="8">
         <f>'balance_raw_37118311'!$B$23</f>
         <v/>
       </c>
-      <c r="C42" s="5">
+      <c r="C42" s="8">
         <f>'balance_raw_37118311'!$C$23</f>
         <v/>
       </c>
-      <c r="D42" s="5">
+      <c r="D42" s="8">
         <f>'balance_raw_37118311'!$D$23</f>
         <v/>
       </c>
-      <c r="E42" s="5">
+      <c r="E42" s="8">
         <f>'balance_raw_37118311'!$E$23</f>
         <v/>
       </c>
-      <c r="F42" s="5">
+      <c r="F42" s="8">
         <f>'balance_raw_37118311'!$F$23</f>
         <v/>
       </c>
       <c r="G42" t="inlineStr"/>
-      <c r="H42" s="6">
+      <c r="H42" s="9">
         <f>IFERROR(B42/$B$42*100,"")</f>
         <v/>
       </c>
-      <c r="I42" s="6">
+      <c r="I42" s="9">
         <f>IFERROR(C42/$B$42*100,"")</f>
         <v/>
       </c>
-      <c r="J42" s="6">
+      <c r="J42" s="9">
         <f>IFERROR(D42/$B$42*100,"")</f>
         <v/>
       </c>
-      <c r="K42" s="6">
+      <c r="K42" s="9">
         <f>IFERROR(E42/$B$42*100,"")</f>
         <v/>
       </c>
-      <c r="L42" s="6">
+      <c r="L42" s="9">
         <f>IFERROR(F42/$B$42*100,"")</f>
         <v/>
       </c>
@@ -2492,7 +2492,7 @@
     <row r="43" ht="16" customHeight="1">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>Udskudt skatteaktiv</t>
+          <t>Værdipapirer</t>
         </is>
       </c>
       <c r="B43" s="11">
@@ -2540,7 +2540,7 @@
     <row r="44" ht="16" customHeight="1">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>Tilgodehavende skat hos tilknyttede virksomheder</t>
+          <t>Likvide beholdninger</t>
         </is>
       </c>
       <c r="B44" s="5">
@@ -2586,49 +2586,49 @@
       </c>
     </row>
     <row r="45" ht="16" customHeight="1">
-      <c r="A45" s="10" t="inlineStr">
-        <is>
-          <t>Kortfristede skattetilgodehavender</t>
-        </is>
-      </c>
-      <c r="B45" s="11">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>Omsætningsaktiver</t>
+        </is>
+      </c>
+      <c r="B45" s="8">
         <f>'balance_raw_37118311'!$B$26</f>
         <v/>
       </c>
-      <c r="C45" s="11">
+      <c r="C45" s="8">
         <f>'balance_raw_37118311'!$C$26</f>
         <v/>
       </c>
-      <c r="D45" s="11">
+      <c r="D45" s="8">
         <f>'balance_raw_37118311'!$D$26</f>
         <v/>
       </c>
-      <c r="E45" s="11">
+      <c r="E45" s="8">
         <f>'balance_raw_37118311'!$E$26</f>
         <v/>
       </c>
-      <c r="F45" s="11">
+      <c r="F45" s="8">
         <f>'balance_raw_37118311'!$F$26</f>
         <v/>
       </c>
       <c r="G45" t="inlineStr"/>
-      <c r="H45" s="12">
+      <c r="H45" s="9">
         <f>IFERROR(B45/$B$45*100,"")</f>
         <v/>
       </c>
-      <c r="I45" s="12">
+      <c r="I45" s="9">
         <f>IFERROR(C45/$B$45*100,"")</f>
         <v/>
       </c>
-      <c r="J45" s="12">
+      <c r="J45" s="9">
         <f>IFERROR(D45/$B$45*100,"")</f>
         <v/>
       </c>
-      <c r="K45" s="12">
+      <c r="K45" s="9">
         <f>IFERROR(E45/$B$45*100,"")</f>
         <v/>
       </c>
-      <c r="L45" s="12">
+      <c r="L45" s="9">
         <f>IFERROR(F45/$B$45*100,"")</f>
         <v/>
       </c>
@@ -2636,7 +2636,7 @@
     <row r="46" ht="16" customHeight="1">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>Tilgodehavender</t>
+          <t>Aktiver</t>
         </is>
       </c>
       <c r="B46" s="8">
@@ -2681,240 +2681,240 @@
         <v/>
       </c>
     </row>
-    <row r="47" ht="16" customHeight="1">
-      <c r="A47" s="10" t="inlineStr">
-        <is>
-          <t>Værdipapirer</t>
-        </is>
-      </c>
-      <c r="B47" s="11">
+    <row r="48" ht="22" customHeight="1">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>PASSIVER t.kr.</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" s="3" t="n">
+        <v>2021</v>
+      </c>
+      <c r="I48" s="3" t="n">
+        <v>2022</v>
+      </c>
+      <c r="J48" s="3" t="n">
+        <v>2023</v>
+      </c>
+      <c r="K48" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L48" s="3" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="49" ht="16" customHeight="1">
+      <c r="A49" s="10" t="inlineStr">
+        <is>
+          <t>Selskabskapital</t>
+        </is>
+      </c>
+      <c r="B49" s="11">
         <f>'balance_raw_37118311'!$B$28</f>
         <v/>
       </c>
-      <c r="C47" s="11">
+      <c r="C49" s="11">
         <f>'balance_raw_37118311'!$C$28</f>
         <v/>
       </c>
-      <c r="D47" s="11">
+      <c r="D49" s="11">
         <f>'balance_raw_37118311'!$D$28</f>
         <v/>
       </c>
-      <c r="E47" s="11">
+      <c r="E49" s="11">
         <f>'balance_raw_37118311'!$E$28</f>
         <v/>
       </c>
-      <c r="F47" s="11">
+      <c r="F49" s="11">
         <f>'balance_raw_37118311'!$F$28</f>
         <v/>
       </c>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" s="12">
-        <f>IFERROR(B47/$B$47*100,"")</f>
-        <v/>
-      </c>
-      <c r="I47" s="12">
-        <f>IFERROR(C47/$B$47*100,"")</f>
-        <v/>
-      </c>
-      <c r="J47" s="12">
-        <f>IFERROR(D47/$B$47*100,"")</f>
-        <v/>
-      </c>
-      <c r="K47" s="12">
-        <f>IFERROR(E47/$B$47*100,"")</f>
-        <v/>
-      </c>
-      <c r="L47" s="12">
-        <f>IFERROR(F47/$B$47*100,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48" ht="16" customHeight="1">
-      <c r="A48" s="4" t="inlineStr">
-        <is>
-          <t>Likvide beholdninger</t>
-        </is>
-      </c>
-      <c r="B48" s="5">
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" s="12">
+        <f>IFERROR(B49/$B$49*100,"")</f>
+        <v/>
+      </c>
+      <c r="I49" s="12">
+        <f>IFERROR(C49/$B$49*100,"")</f>
+        <v/>
+      </c>
+      <c r="J49" s="12">
+        <f>IFERROR(D49/$B$49*100,"")</f>
+        <v/>
+      </c>
+      <c r="K49" s="12">
+        <f>IFERROR(E49/$B$49*100,"")</f>
+        <v/>
+      </c>
+      <c r="L49" s="12">
+        <f>IFERROR(F49/$B$49*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50" ht="16" customHeight="1">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Reserve for nettoopskrivning (indre værdis metode)</t>
+        </is>
+      </c>
+      <c r="B50" s="5">
         <f>'balance_raw_37118311'!$B$29</f>
         <v/>
       </c>
-      <c r="C48" s="5">
+      <c r="C50" s="5">
         <f>'balance_raw_37118311'!$C$29</f>
         <v/>
       </c>
-      <c r="D48" s="5">
+      <c r="D50" s="5">
         <f>'balance_raw_37118311'!$D$29</f>
         <v/>
       </c>
-      <c r="E48" s="5">
+      <c r="E50" s="5">
         <f>'balance_raw_37118311'!$E$29</f>
         <v/>
       </c>
-      <c r="F48" s="5">
+      <c r="F50" s="5">
         <f>'balance_raw_37118311'!$F$29</f>
         <v/>
       </c>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" s="6">
-        <f>IFERROR(B48/$B$48*100,"")</f>
-        <v/>
-      </c>
-      <c r="I48" s="6">
-        <f>IFERROR(C48/$B$48*100,"")</f>
-        <v/>
-      </c>
-      <c r="J48" s="6">
-        <f>IFERROR(D48/$B$48*100,"")</f>
-        <v/>
-      </c>
-      <c r="K48" s="6">
-        <f>IFERROR(E48/$B$48*100,"")</f>
-        <v/>
-      </c>
-      <c r="L48" s="6">
-        <f>IFERROR(F48/$B$48*100,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="49" ht="16" customHeight="1">
-      <c r="A49" s="7" t="inlineStr">
-        <is>
-          <t>Omsætningsaktiver</t>
-        </is>
-      </c>
-      <c r="B49" s="8">
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" s="6">
+        <f>IFERROR(B50/$B$50*100,"")</f>
+        <v/>
+      </c>
+      <c r="I50" s="6">
+        <f>IFERROR(C50/$B$50*100,"")</f>
+        <v/>
+      </c>
+      <c r="J50" s="6">
+        <f>IFERROR(D50/$B$50*100,"")</f>
+        <v/>
+      </c>
+      <c r="K50" s="6">
+        <f>IFERROR(E50/$B$50*100,"")</f>
+        <v/>
+      </c>
+      <c r="L50" s="6">
+        <f>IFERROR(F50/$B$50*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51" ht="16" customHeight="1">
+      <c r="A51" s="10" t="inlineStr">
+        <is>
+          <t>Reserve for udviklingsomkostninger</t>
+        </is>
+      </c>
+      <c r="B51" s="11">
         <f>'balance_raw_37118311'!$B$30</f>
         <v/>
       </c>
-      <c r="C49" s="8">
+      <c r="C51" s="11">
         <f>'balance_raw_37118311'!$C$30</f>
         <v/>
       </c>
-      <c r="D49" s="8">
+      <c r="D51" s="11">
         <f>'balance_raw_37118311'!$D$30</f>
         <v/>
       </c>
-      <c r="E49" s="8">
+      <c r="E51" s="11">
         <f>'balance_raw_37118311'!$E$30</f>
         <v/>
       </c>
-      <c r="F49" s="8">
+      <c r="F51" s="11">
         <f>'balance_raw_37118311'!$F$30</f>
         <v/>
       </c>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" s="9">
-        <f>IFERROR(B49/$B$49*100,"")</f>
-        <v/>
-      </c>
-      <c r="I49" s="9">
-        <f>IFERROR(C49/$B$49*100,"")</f>
-        <v/>
-      </c>
-      <c r="J49" s="9">
-        <f>IFERROR(D49/$B$49*100,"")</f>
-        <v/>
-      </c>
-      <c r="K49" s="9">
-        <f>IFERROR(E49/$B$49*100,"")</f>
-        <v/>
-      </c>
-      <c r="L49" s="9">
-        <f>IFERROR(F49/$B$49*100,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="50" ht="16" customHeight="1">
-      <c r="A50" s="7" t="inlineStr">
-        <is>
-          <t>Aktiver</t>
-        </is>
-      </c>
-      <c r="B50" s="8">
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" s="12">
+        <f>IFERROR(B51/$B$51*100,"")</f>
+        <v/>
+      </c>
+      <c r="I51" s="12">
+        <f>IFERROR(C51/$B$51*100,"")</f>
+        <v/>
+      </c>
+      <c r="J51" s="12">
+        <f>IFERROR(D51/$B$51*100,"")</f>
+        <v/>
+      </c>
+      <c r="K51" s="12">
+        <f>IFERROR(E51/$B$51*100,"")</f>
+        <v/>
+      </c>
+      <c r="L51" s="12">
+        <f>IFERROR(F51/$B$51*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52" ht="16" customHeight="1">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Reserve for sikringstransaktioner</t>
+        </is>
+      </c>
+      <c r="B52" s="5">
         <f>'balance_raw_37118311'!$B$31</f>
         <v/>
       </c>
-      <c r="C50" s="8">
+      <c r="C52" s="5">
         <f>'balance_raw_37118311'!$C$31</f>
         <v/>
       </c>
-      <c r="D50" s="8">
+      <c r="D52" s="5">
         <f>'balance_raw_37118311'!$D$31</f>
         <v/>
       </c>
-      <c r="E50" s="8">
+      <c r="E52" s="5">
         <f>'balance_raw_37118311'!$E$31</f>
         <v/>
       </c>
-      <c r="F50" s="8">
+      <c r="F52" s="5">
         <f>'balance_raw_37118311'!$F$31</f>
         <v/>
       </c>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" s="9">
-        <f>IFERROR(B50/$B$50*100,"")</f>
-        <v/>
-      </c>
-      <c r="I50" s="9">
-        <f>IFERROR(C50/$B$50*100,"")</f>
-        <v/>
-      </c>
-      <c r="J50" s="9">
-        <f>IFERROR(D50/$B$50*100,"")</f>
-        <v/>
-      </c>
-      <c r="K50" s="9">
-        <f>IFERROR(E50/$B$50*100,"")</f>
-        <v/>
-      </c>
-      <c r="L50" s="9">
-        <f>IFERROR(F50/$B$50*100,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="52" ht="22" customHeight="1">
-      <c r="A52" s="3" t="inlineStr">
-        <is>
-          <t>PASSIVER t.kr.</t>
-        </is>
-      </c>
-      <c r="B52" s="3" t="n">
-        <v>2020</v>
-      </c>
-      <c r="C52" s="3" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D52" s="3" t="n">
-        <v>2022</v>
-      </c>
-      <c r="E52" s="3" t="n">
-        <v>2023</v>
-      </c>
-      <c r="F52" s="3" t="n">
-        <v>2024</v>
-      </c>
       <c r="G52" t="inlineStr"/>
-      <c r="H52" s="3" t="n">
-        <v>2020</v>
-      </c>
-      <c r="I52" s="3" t="n">
-        <v>2021</v>
-      </c>
-      <c r="J52" s="3" t="n">
-        <v>2022</v>
-      </c>
-      <c r="K52" s="3" t="n">
-        <v>2023</v>
-      </c>
-      <c r="L52" s="3" t="n">
-        <v>2024</v>
+      <c r="H52" s="6">
+        <f>IFERROR(B52/$B$52*100,"")</f>
+        <v/>
+      </c>
+      <c r="I52" s="6">
+        <f>IFERROR(C52/$B$52*100,"")</f>
+        <v/>
+      </c>
+      <c r="J52" s="6">
+        <f>IFERROR(D52/$B$52*100,"")</f>
+        <v/>
+      </c>
+      <c r="K52" s="6">
+        <f>IFERROR(E52/$B$52*100,"")</f>
+        <v/>
+      </c>
+      <c r="L52" s="6">
+        <f>IFERROR(F52/$B$52*100,"")</f>
+        <v/>
       </c>
     </row>
     <row r="53" ht="16" customHeight="1">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>Selskabskapital</t>
+          <t>Andre reserver</t>
         </is>
       </c>
       <c r="B53" s="11">
@@ -2962,7 +2962,7 @@
     <row r="54" ht="16" customHeight="1">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>Reserve for nettoopskrivning (indre værdis metode)</t>
+          <t>Overført resultat</t>
         </is>
       </c>
       <c r="B54" s="5">
@@ -3008,49 +3008,49 @@
       </c>
     </row>
     <row r="55" ht="16" customHeight="1">
-      <c r="A55" s="10" t="inlineStr">
-        <is>
-          <t>Reserve for udviklingsomkostninger</t>
-        </is>
-      </c>
-      <c r="B55" s="11">
+      <c r="A55" s="7" t="inlineStr">
+        <is>
+          <t>Egenkapital i alt</t>
+        </is>
+      </c>
+      <c r="B55" s="8">
         <f>'balance_raw_37118311'!$B$34</f>
         <v/>
       </c>
-      <c r="C55" s="11">
+      <c r="C55" s="8">
         <f>'balance_raw_37118311'!$C$34</f>
         <v/>
       </c>
-      <c r="D55" s="11">
+      <c r="D55" s="8">
         <f>'balance_raw_37118311'!$D$34</f>
         <v/>
       </c>
-      <c r="E55" s="11">
+      <c r="E55" s="8">
         <f>'balance_raw_37118311'!$E$34</f>
         <v/>
       </c>
-      <c r="F55" s="11">
+      <c r="F55" s="8">
         <f>'balance_raw_37118311'!$F$34</f>
         <v/>
       </c>
       <c r="G55" t="inlineStr"/>
-      <c r="H55" s="12">
+      <c r="H55" s="9">
         <f>IFERROR(B55/$B$55*100,"")</f>
         <v/>
       </c>
-      <c r="I55" s="12">
+      <c r="I55" s="9">
         <f>IFERROR(C55/$B$55*100,"")</f>
         <v/>
       </c>
-      <c r="J55" s="12">
+      <c r="J55" s="9">
         <f>IFERROR(D55/$B$55*100,"")</f>
         <v/>
       </c>
-      <c r="K55" s="12">
+      <c r="K55" s="9">
         <f>IFERROR(E55/$B$55*100,"")</f>
         <v/>
       </c>
-      <c r="L55" s="12">
+      <c r="L55" s="9">
         <f>IFERROR(F55/$B$55*100,"")</f>
         <v/>
       </c>
@@ -3058,7 +3058,7 @@
     <row r="56" ht="16" customHeight="1">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>Reserve for sikringstransaktioner</t>
+          <t>Hensættelse til udskudt skat</t>
         </is>
       </c>
       <c r="B56" s="5">
@@ -3104,49 +3104,49 @@
       </c>
     </row>
     <row r="57" ht="16" customHeight="1">
-      <c r="A57" s="10" t="inlineStr">
-        <is>
-          <t>Andre reserver</t>
-        </is>
-      </c>
-      <c r="B57" s="11">
+      <c r="A57" s="7" t="inlineStr">
+        <is>
+          <t>Hensatte forpligtelser</t>
+        </is>
+      </c>
+      <c r="B57" s="8">
         <f>'balance_raw_37118311'!$B$36</f>
         <v/>
       </c>
-      <c r="C57" s="11">
+      <c r="C57" s="8">
         <f>'balance_raw_37118311'!$C$36</f>
         <v/>
       </c>
-      <c r="D57" s="11">
+      <c r="D57" s="8">
         <f>'balance_raw_37118311'!$D$36</f>
         <v/>
       </c>
-      <c r="E57" s="11">
+      <c r="E57" s="8">
         <f>'balance_raw_37118311'!$E$36</f>
         <v/>
       </c>
-      <c r="F57" s="11">
+      <c r="F57" s="8">
         <f>'balance_raw_37118311'!$F$36</f>
         <v/>
       </c>
       <c r="G57" t="inlineStr"/>
-      <c r="H57" s="12">
+      <c r="H57" s="9">
         <f>IFERROR(B57/$B$57*100,"")</f>
         <v/>
       </c>
-      <c r="I57" s="12">
+      <c r="I57" s="9">
         <f>IFERROR(C57/$B$57*100,"")</f>
         <v/>
       </c>
-      <c r="J57" s="12">
+      <c r="J57" s="9">
         <f>IFERROR(D57/$B$57*100,"")</f>
         <v/>
       </c>
-      <c r="K57" s="12">
+      <c r="K57" s="9">
         <f>IFERROR(E57/$B$57*100,"")</f>
         <v/>
       </c>
-      <c r="L57" s="12">
+      <c r="L57" s="9">
         <f>IFERROR(F57/$B$57*100,"")</f>
         <v/>
       </c>
@@ -3154,7 +3154,7 @@
     <row r="58" ht="16" customHeight="1">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>Overført resultat</t>
+          <t>Ansvarlig lånekapital (langfristet)</t>
         </is>
       </c>
       <c r="B58" s="5">
@@ -3200,49 +3200,49 @@
       </c>
     </row>
     <row r="59" ht="16" customHeight="1">
-      <c r="A59" s="7" t="inlineStr">
-        <is>
-          <t>Egenkapital i alt</t>
-        </is>
-      </c>
-      <c r="B59" s="8">
+      <c r="A59" s="10" t="inlineStr">
+        <is>
+          <t>Langfristede lån</t>
+        </is>
+      </c>
+      <c r="B59" s="11">
         <f>'balance_raw_37118311'!$B$38</f>
         <v/>
       </c>
-      <c r="C59" s="8">
+      <c r="C59" s="11">
         <f>'balance_raw_37118311'!$C$38</f>
         <v/>
       </c>
-      <c r="D59" s="8">
+      <c r="D59" s="11">
         <f>'balance_raw_37118311'!$D$38</f>
         <v/>
       </c>
-      <c r="E59" s="8">
+      <c r="E59" s="11">
         <f>'balance_raw_37118311'!$E$38</f>
         <v/>
       </c>
-      <c r="F59" s="8">
+      <c r="F59" s="11">
         <f>'balance_raw_37118311'!$F$38</f>
         <v/>
       </c>
       <c r="G59" t="inlineStr"/>
-      <c r="H59" s="9">
+      <c r="H59" s="12">
         <f>IFERROR(B59/$B$59*100,"")</f>
         <v/>
       </c>
-      <c r="I59" s="9">
+      <c r="I59" s="12">
         <f>IFERROR(C59/$B$59*100,"")</f>
         <v/>
       </c>
-      <c r="J59" s="9">
+      <c r="J59" s="12">
         <f>IFERROR(D59/$B$59*100,"")</f>
         <v/>
       </c>
-      <c r="K59" s="9">
+      <c r="K59" s="12">
         <f>IFERROR(E59/$B$59*100,"")</f>
         <v/>
       </c>
-      <c r="L59" s="9">
+      <c r="L59" s="12">
         <f>IFERROR(F59/$B$59*100,"")</f>
         <v/>
       </c>
@@ -3250,7 +3250,7 @@
     <row r="60" ht="16" customHeight="1">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>Hensættelse til udskudt skat</t>
+          <t>Leasingforpligtelser (langfristet)</t>
         </is>
       </c>
       <c r="B60" s="5">
@@ -3296,97 +3296,97 @@
       </c>
     </row>
     <row r="61" ht="16" customHeight="1">
-      <c r="A61" s="7" t="inlineStr">
-        <is>
-          <t>Hensatte forpligtelser</t>
-        </is>
-      </c>
-      <c r="B61" s="8">
+      <c r="A61" s="10" t="inlineStr">
+        <is>
+          <t>Anden gæld (langfristet)</t>
+        </is>
+      </c>
+      <c r="B61" s="11">
         <f>'balance_raw_37118311'!$B$40</f>
         <v/>
       </c>
-      <c r="C61" s="8">
+      <c r="C61" s="11">
         <f>'balance_raw_37118311'!$C$40</f>
         <v/>
       </c>
-      <c r="D61" s="8">
+      <c r="D61" s="11">
         <f>'balance_raw_37118311'!$D$40</f>
         <v/>
       </c>
-      <c r="E61" s="8">
+      <c r="E61" s="11">
         <f>'balance_raw_37118311'!$E$40</f>
         <v/>
       </c>
-      <c r="F61" s="8">
+      <c r="F61" s="11">
         <f>'balance_raw_37118311'!$F$40</f>
         <v/>
       </c>
       <c r="G61" t="inlineStr"/>
-      <c r="H61" s="9">
+      <c r="H61" s="12">
         <f>IFERROR(B61/$B$61*100,"")</f>
         <v/>
       </c>
-      <c r="I61" s="9">
+      <c r="I61" s="12">
         <f>IFERROR(C61/$B$61*100,"")</f>
         <v/>
       </c>
-      <c r="J61" s="9">
+      <c r="J61" s="12">
         <f>IFERROR(D61/$B$61*100,"")</f>
         <v/>
       </c>
-      <c r="K61" s="9">
+      <c r="K61" s="12">
         <f>IFERROR(E61/$B$61*100,"")</f>
         <v/>
       </c>
-      <c r="L61" s="9">
+      <c r="L61" s="12">
         <f>IFERROR(F61/$B$61*100,"")</f>
         <v/>
       </c>
     </row>
     <row r="62" ht="16" customHeight="1">
-      <c r="A62" s="4" t="inlineStr">
-        <is>
-          <t>Ansvarlig lånekapital (langfristet)</t>
-        </is>
-      </c>
-      <c r="B62" s="5">
+      <c r="A62" s="7" t="inlineStr">
+        <is>
+          <t>Langfristede gældsforpligtelser</t>
+        </is>
+      </c>
+      <c r="B62" s="8">
         <f>'balance_raw_37118311'!$B$41</f>
         <v/>
       </c>
-      <c r="C62" s="5">
+      <c r="C62" s="8">
         <f>'balance_raw_37118311'!$C$41</f>
         <v/>
       </c>
-      <c r="D62" s="5">
+      <c r="D62" s="8">
         <f>'balance_raw_37118311'!$D$41</f>
         <v/>
       </c>
-      <c r="E62" s="5">
+      <c r="E62" s="8">
         <f>'balance_raw_37118311'!$E$41</f>
         <v/>
       </c>
-      <c r="F62" s="5">
+      <c r="F62" s="8">
         <f>'balance_raw_37118311'!$F$41</f>
         <v/>
       </c>
       <c r="G62" t="inlineStr"/>
-      <c r="H62" s="6">
+      <c r="H62" s="9">
         <f>IFERROR(B62/$B$62*100,"")</f>
         <v/>
       </c>
-      <c r="I62" s="6">
+      <c r="I62" s="9">
         <f>IFERROR(C62/$B$62*100,"")</f>
         <v/>
       </c>
-      <c r="J62" s="6">
+      <c r="J62" s="9">
         <f>IFERROR(D62/$B$62*100,"")</f>
         <v/>
       </c>
-      <c r="K62" s="6">
+      <c r="K62" s="9">
         <f>IFERROR(E62/$B$62*100,"")</f>
         <v/>
       </c>
-      <c r="L62" s="6">
+      <c r="L62" s="9">
         <f>IFERROR(F62/$B$62*100,"")</f>
         <v/>
       </c>
@@ -3394,7 +3394,7 @@
     <row r="63" ht="16" customHeight="1">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>Langfristede lån</t>
+          <t>Ansvarlig lånekapital (kortfristet)</t>
         </is>
       </c>
       <c r="B63" s="11">
@@ -3442,7 +3442,7 @@
     <row r="64" ht="16" customHeight="1">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>Leasingforpligtelser (langfristet)</t>
+          <t>Kortfristet del af langfristede gældsforpligtelser</t>
         </is>
       </c>
       <c r="B64" s="5">
@@ -3490,7 +3490,7 @@
     <row r="65" ht="16" customHeight="1">
       <c r="A65" s="10" t="inlineStr">
         <is>
-          <t>Anden gæld (langfristet)</t>
+          <t>Kreditinstitutter</t>
         </is>
       </c>
       <c r="B65" s="11">
@@ -3536,49 +3536,49 @@
       </c>
     </row>
     <row r="66" ht="16" customHeight="1">
-      <c r="A66" s="7" t="inlineStr">
-        <is>
-          <t>Langfristede gældsforpligtelser</t>
-        </is>
-      </c>
-      <c r="B66" s="8">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>Leasingforpligtelser (kortfristet)</t>
+        </is>
+      </c>
+      <c r="B66" s="5">
         <f>'balance_raw_37118311'!$B$45</f>
         <v/>
       </c>
-      <c r="C66" s="8">
+      <c r="C66" s="5">
         <f>'balance_raw_37118311'!$C$45</f>
         <v/>
       </c>
-      <c r="D66" s="8">
+      <c r="D66" s="5">
         <f>'balance_raw_37118311'!$D$45</f>
         <v/>
       </c>
-      <c r="E66" s="8">
+      <c r="E66" s="5">
         <f>'balance_raw_37118311'!$E$45</f>
         <v/>
       </c>
-      <c r="F66" s="8">
+      <c r="F66" s="5">
         <f>'balance_raw_37118311'!$F$45</f>
         <v/>
       </c>
       <c r="G66" t="inlineStr"/>
-      <c r="H66" s="9">
+      <c r="H66" s="6">
         <f>IFERROR(B66/$B$66*100,"")</f>
         <v/>
       </c>
-      <c r="I66" s="9">
+      <c r="I66" s="6">
         <f>IFERROR(C66/$B$66*100,"")</f>
         <v/>
       </c>
-      <c r="J66" s="9">
+      <c r="J66" s="6">
         <f>IFERROR(D66/$B$66*100,"")</f>
         <v/>
       </c>
-      <c r="K66" s="9">
+      <c r="K66" s="6">
         <f>IFERROR(E66/$B$66*100,"")</f>
         <v/>
       </c>
-      <c r="L66" s="9">
+      <c r="L66" s="6">
         <f>IFERROR(F66/$B$66*100,"")</f>
         <v/>
       </c>
@@ -3586,7 +3586,7 @@
     <row r="67" ht="16" customHeight="1">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>Ansvarlig lånekapital (kortfristet)</t>
+          <t>Leverandører af varer og tjenesteydelser</t>
         </is>
       </c>
       <c r="B67" s="11">
@@ -3634,7 +3634,7 @@
     <row r="68" ht="16" customHeight="1">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>Kortfristet del af langfristede gældsforpligtelser</t>
+          <t>Gæld til tilknyttede virksomheder</t>
         </is>
       </c>
       <c r="B68" s="5">
@@ -3682,7 +3682,7 @@
     <row r="69" ht="16" customHeight="1">
       <c r="A69" s="10" t="inlineStr">
         <is>
-          <t>Kreditinstitutter</t>
+          <t>Gæld til selskabsdeltagere og ledelse</t>
         </is>
       </c>
       <c r="B69" s="11">
@@ -3730,7 +3730,7 @@
     <row r="70" ht="16" customHeight="1">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>Leasingforpligtelser (kortfristet)</t>
+          <t>Selskabsskat</t>
         </is>
       </c>
       <c r="B70" s="5">
@@ -3778,7 +3778,7 @@
     <row r="71" ht="16" customHeight="1">
       <c r="A71" s="10" t="inlineStr">
         <is>
-          <t>Leverandører af varer og tjenesteydelser</t>
+          <t>Gæld til tilknyttede virksomheder vedr. selskabsskat</t>
         </is>
       </c>
       <c r="B71" s="11">
@@ -3826,7 +3826,7 @@
     <row r="72" ht="16" customHeight="1">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>Gæld til tilknyttede virksomheder</t>
+          <t>Anden gæld (kortfristet)</t>
         </is>
       </c>
       <c r="B72" s="5">
@@ -3874,7 +3874,7 @@
     <row r="73" ht="16" customHeight="1">
       <c r="A73" s="10" t="inlineStr">
         <is>
-          <t>Gæld til selskabsdeltagere og ledelse</t>
+          <t>Periodeafgrænsningsposter (passiver)</t>
         </is>
       </c>
       <c r="B73" s="11">
@@ -3920,337 +3920,263 @@
       </c>
     </row>
     <row r="74" ht="16" customHeight="1">
-      <c r="A74" s="4" t="inlineStr">
-        <is>
-          <t>Selskabsskat</t>
-        </is>
-      </c>
-      <c r="B74" s="5">
+      <c r="A74" s="7" t="inlineStr">
+        <is>
+          <t>Kortfristede gældsforpligtelser</t>
+        </is>
+      </c>
+      <c r="B74" s="8">
         <f>'balance_raw_37118311'!$B$53</f>
         <v/>
       </c>
-      <c r="C74" s="5">
+      <c r="C74" s="8">
         <f>'balance_raw_37118311'!$C$53</f>
         <v/>
       </c>
-      <c r="D74" s="5">
+      <c r="D74" s="8">
         <f>'balance_raw_37118311'!$D$53</f>
         <v/>
       </c>
-      <c r="E74" s="5">
+      <c r="E74" s="8">
         <f>'balance_raw_37118311'!$E$53</f>
         <v/>
       </c>
-      <c r="F74" s="5">
+      <c r="F74" s="8">
         <f>'balance_raw_37118311'!$F$53</f>
         <v/>
       </c>
       <c r="G74" t="inlineStr"/>
-      <c r="H74" s="6">
+      <c r="H74" s="9">
         <f>IFERROR(B74/$B$74*100,"")</f>
         <v/>
       </c>
-      <c r="I74" s="6">
+      <c r="I74" s="9">
         <f>IFERROR(C74/$B$74*100,"")</f>
         <v/>
       </c>
-      <c r="J74" s="6">
+      <c r="J74" s="9">
         <f>IFERROR(D74/$B$74*100,"")</f>
         <v/>
       </c>
-      <c r="K74" s="6">
+      <c r="K74" s="9">
         <f>IFERROR(E74/$B$74*100,"")</f>
         <v/>
       </c>
-      <c r="L74" s="6">
+      <c r="L74" s="9">
         <f>IFERROR(F74/$B$74*100,"")</f>
         <v/>
       </c>
     </row>
     <row r="75" ht="16" customHeight="1">
-      <c r="A75" s="10" t="inlineStr">
-        <is>
-          <t>Gæld til tilknyttede virksomheder vedr. selskabsskat</t>
-        </is>
-      </c>
-      <c r="B75" s="11">
+      <c r="A75" s="7" t="inlineStr">
+        <is>
+          <t>Gældsforpligtelser</t>
+        </is>
+      </c>
+      <c r="B75" s="8">
         <f>'balance_raw_37118311'!$B$54</f>
         <v/>
       </c>
-      <c r="C75" s="11">
+      <c r="C75" s="8">
         <f>'balance_raw_37118311'!$C$54</f>
         <v/>
       </c>
-      <c r="D75" s="11">
+      <c r="D75" s="8">
         <f>'balance_raw_37118311'!$D$54</f>
         <v/>
       </c>
-      <c r="E75" s="11">
+      <c r="E75" s="8">
         <f>'balance_raw_37118311'!$E$54</f>
         <v/>
       </c>
-      <c r="F75" s="11">
+      <c r="F75" s="8">
         <f>'balance_raw_37118311'!$F$54</f>
         <v/>
       </c>
       <c r="G75" t="inlineStr"/>
-      <c r="H75" s="12">
+      <c r="H75" s="9">
         <f>IFERROR(B75/$B$75*100,"")</f>
         <v/>
       </c>
-      <c r="I75" s="12">
+      <c r="I75" s="9">
         <f>IFERROR(C75/$B$75*100,"")</f>
         <v/>
       </c>
-      <c r="J75" s="12">
+      <c r="J75" s="9">
         <f>IFERROR(D75/$B$75*100,"")</f>
         <v/>
       </c>
-      <c r="K75" s="12">
+      <c r="K75" s="9">
         <f>IFERROR(E75/$B$75*100,"")</f>
         <v/>
       </c>
-      <c r="L75" s="12">
+      <c r="L75" s="9">
         <f>IFERROR(F75/$B$75*100,"")</f>
         <v/>
       </c>
     </row>
     <row r="76" ht="16" customHeight="1">
-      <c r="A76" s="4" t="inlineStr">
-        <is>
-          <t>Anden gæld (kortfristet)</t>
-        </is>
-      </c>
-      <c r="B76" s="5">
+      <c r="A76" s="7" t="inlineStr">
+        <is>
+          <t>Passiver</t>
+        </is>
+      </c>
+      <c r="B76" s="8">
         <f>'balance_raw_37118311'!$B$55</f>
         <v/>
       </c>
-      <c r="C76" s="5">
+      <c r="C76" s="8">
         <f>'balance_raw_37118311'!$C$55</f>
         <v/>
       </c>
-      <c r="D76" s="5">
+      <c r="D76" s="8">
         <f>'balance_raw_37118311'!$D$55</f>
         <v/>
       </c>
-      <c r="E76" s="5">
+      <c r="E76" s="8">
         <f>'balance_raw_37118311'!$E$55</f>
         <v/>
       </c>
-      <c r="F76" s="5">
+      <c r="F76" s="8">
         <f>'balance_raw_37118311'!$F$55</f>
         <v/>
       </c>
       <c r="G76" t="inlineStr"/>
-      <c r="H76" s="6">
+      <c r="H76" s="9">
         <f>IFERROR(B76/$B$76*100,"")</f>
         <v/>
       </c>
-      <c r="I76" s="6">
+      <c r="I76" s="9">
         <f>IFERROR(C76/$B$76*100,"")</f>
         <v/>
       </c>
-      <c r="J76" s="6">
+      <c r="J76" s="9">
         <f>IFERROR(D76/$B$76*100,"")</f>
         <v/>
       </c>
-      <c r="K76" s="6">
+      <c r="K76" s="9">
         <f>IFERROR(E76/$B$76*100,"")</f>
         <v/>
       </c>
-      <c r="L76" s="6">
+      <c r="L76" s="9">
         <f>IFERROR(F76/$B$76*100,"")</f>
         <v/>
       </c>
     </row>
-    <row r="77" ht="16" customHeight="1">
-      <c r="A77" s="10" t="inlineStr">
-        <is>
-          <t>Periodeafgrænsningsposter (passiver)</t>
-        </is>
-      </c>
-      <c r="B77" s="11">
-        <f>'balance_raw_37118311'!$B$56</f>
-        <v/>
-      </c>
-      <c r="C77" s="11">
-        <f>'balance_raw_37118311'!$C$56</f>
-        <v/>
-      </c>
-      <c r="D77" s="11">
-        <f>'balance_raw_37118311'!$D$56</f>
-        <v/>
-      </c>
-      <c r="E77" s="11">
-        <f>'balance_raw_37118311'!$E$56</f>
-        <v/>
-      </c>
-      <c r="F77" s="11">
-        <f>'balance_raw_37118311'!$F$56</f>
-        <v/>
-      </c>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" s="12">
-        <f>IFERROR(B77/$B$77*100,"")</f>
-        <v/>
-      </c>
-      <c r="I77" s="12">
-        <f>IFERROR(C77/$B$77*100,"")</f>
-        <v/>
-      </c>
-      <c r="J77" s="12">
-        <f>IFERROR(D77/$B$77*100,"")</f>
-        <v/>
-      </c>
-      <c r="K77" s="12">
-        <f>IFERROR(E77/$B$77*100,"")</f>
-        <v/>
-      </c>
-      <c r="L77" s="12">
-        <f>IFERROR(F77/$B$77*100,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="78" ht="16" customHeight="1">
-      <c r="A78" s="7" t="inlineStr">
-        <is>
-          <t>Kortfristede gældsforpligtelser</t>
-        </is>
-      </c>
-      <c r="B78" s="8">
-        <f>'balance_raw_37118311'!$B$57</f>
-        <v/>
-      </c>
-      <c r="C78" s="8">
-        <f>'balance_raw_37118311'!$C$57</f>
-        <v/>
-      </c>
-      <c r="D78" s="8">
-        <f>'balance_raw_37118311'!$D$57</f>
-        <v/>
-      </c>
-      <c r="E78" s="8">
-        <f>'balance_raw_37118311'!$E$57</f>
-        <v/>
-      </c>
-      <c r="F78" s="8">
-        <f>'balance_raw_37118311'!$F$57</f>
-        <v/>
-      </c>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" s="9">
-        <f>IFERROR(B78/$B$78*100,"")</f>
-        <v/>
-      </c>
-      <c r="I78" s="9">
-        <f>IFERROR(C78/$B$78*100,"")</f>
-        <v/>
-      </c>
-      <c r="J78" s="9">
-        <f>IFERROR(D78/$B$78*100,"")</f>
-        <v/>
-      </c>
-      <c r="K78" s="9">
-        <f>IFERROR(E78/$B$78*100,"")</f>
-        <v/>
-      </c>
-      <c r="L78" s="9">
-        <f>IFERROR(F78/$B$78*100,"")</f>
-        <v/>
+    <row r="78" ht="22" customHeight="1">
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t>NØGLEOPLYSNINGER</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C78" s="3" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D78" s="3" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E78" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F78" s="3" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="79" ht="16" customHeight="1">
-      <c r="A79" s="7" t="inlineStr">
-        <is>
-          <t>Gældsforpligtelser</t>
-        </is>
-      </c>
-      <c r="B79" s="8">
-        <f>'balance_raw_37118311'!$B$58</f>
-        <v/>
-      </c>
-      <c r="C79" s="8">
-        <f>'balance_raw_37118311'!$C$58</f>
-        <v/>
-      </c>
-      <c r="D79" s="8">
-        <f>'balance_raw_37118311'!$D$58</f>
-        <v/>
-      </c>
-      <c r="E79" s="8">
-        <f>'balance_raw_37118311'!$E$58</f>
-        <v/>
-      </c>
-      <c r="F79" s="8">
-        <f>'balance_raw_37118311'!$F$58</f>
+      <c r="A79" s="10" t="inlineStr">
+        <is>
+          <t>Gns. antal medarbejdere</t>
+        </is>
+      </c>
+      <c r="B79" s="11">
+        <f>'res_raw_37118311'!$B$17</f>
+        <v/>
+      </c>
+      <c r="C79" s="11">
+        <f>'res_raw_37118311'!$C$17</f>
+        <v/>
+      </c>
+      <c r="D79" s="11">
+        <f>'res_raw_37118311'!$D$17</f>
+        <v/>
+      </c>
+      <c r="E79" s="11">
+        <f>'res_raw_37118311'!$E$17</f>
+        <v/>
+      </c>
+      <c r="F79" s="11">
+        <f>'res_raw_37118311'!$F$17</f>
         <v/>
       </c>
       <c r="G79" t="inlineStr"/>
-      <c r="H79" s="9">
+      <c r="H79" s="12">
         <f>IFERROR(B79/$B$79*100,"")</f>
         <v/>
       </c>
-      <c r="I79" s="9">
+      <c r="I79" s="12">
         <f>IFERROR(C79/$B$79*100,"")</f>
         <v/>
       </c>
-      <c r="J79" s="9">
+      <c r="J79" s="12">
         <f>IFERROR(D79/$B$79*100,"")</f>
         <v/>
       </c>
-      <c r="K79" s="9">
+      <c r="K79" s="12">
         <f>IFERROR(E79/$B$79*100,"")</f>
         <v/>
       </c>
-      <c r="L79" s="9">
+      <c r="L79" s="12">
         <f>IFERROR(F79/$B$79*100,"")</f>
         <v/>
       </c>
     </row>
     <row r="80" ht="16" customHeight="1">
-      <c r="A80" s="7" t="inlineStr">
-        <is>
-          <t>Passiver</t>
-        </is>
-      </c>
-      <c r="B80" s="8">
-        <f>'balance_raw_37118311'!$B$59</f>
-        <v/>
-      </c>
-      <c r="C80" s="8">
-        <f>'balance_raw_37118311'!$C$59</f>
-        <v/>
-      </c>
-      <c r="D80" s="8">
-        <f>'balance_raw_37118311'!$D$59</f>
-        <v/>
-      </c>
-      <c r="E80" s="8">
-        <f>'balance_raw_37118311'!$E$59</f>
-        <v/>
-      </c>
-      <c r="F80" s="8">
-        <f>'balance_raw_37118311'!$F$59</f>
+      <c r="A80" s="4" t="inlineStr">
+        <is>
+          <t>Investering i materielle anlægsaktiver</t>
+        </is>
+      </c>
+      <c r="B80" s="5">
+        <f>'res_raw_37118311'!$B$18</f>
+        <v/>
+      </c>
+      <c r="C80" s="5">
+        <f>'res_raw_37118311'!$C$18</f>
+        <v/>
+      </c>
+      <c r="D80" s="5">
+        <f>'res_raw_37118311'!$D$18</f>
+        <v/>
+      </c>
+      <c r="E80" s="5">
+        <f>'res_raw_37118311'!$E$18</f>
+        <v/>
+      </c>
+      <c r="F80" s="5">
+        <f>'res_raw_37118311'!$F$18</f>
         <v/>
       </c>
       <c r="G80" t="inlineStr"/>
-      <c r="H80" s="9">
+      <c r="H80" s="6">
         <f>IFERROR(B80/$B$80*100,"")</f>
         <v/>
       </c>
-      <c r="I80" s="9">
+      <c r="I80" s="6">
         <f>IFERROR(C80/$B$80*100,"")</f>
         <v/>
       </c>
-      <c r="J80" s="9">
+      <c r="J80" s="6">
         <f>IFERROR(D80/$B$80*100,"")</f>
         <v/>
       </c>
-      <c r="K80" s="9">
+      <c r="K80" s="6">
         <f>IFERROR(E80/$B$80*100,"")</f>
         <v/>
       </c>
-      <c r="L80" s="9">
+      <c r="L80" s="6">
         <f>IFERROR(F80/$B$80*100,"")</f>
         <v/>
       </c>
@@ -4258,438 +4184,327 @@
     <row r="82" ht="22" customHeight="1">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>NØGLEOPLYSNINGER</t>
+          <t>NØGLETAL</t>
         </is>
       </c>
       <c r="B82" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C82" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E82" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F82" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="83" ht="16" customHeight="1">
       <c r="A83" s="10" t="inlineStr">
         <is>
-          <t>Gns. antal medarbejdere</t>
-        </is>
-      </c>
-      <c r="B83" s="11">
-        <f>'res_raw_37118311'!$B$17</f>
-        <v/>
-      </c>
-      <c r="C83" s="11">
-        <f>'res_raw_37118311'!$C$17</f>
-        <v/>
-      </c>
-      <c r="D83" s="11">
-        <f>'res_raw_37118311'!$D$17</f>
-        <v/>
-      </c>
-      <c r="E83" s="11">
-        <f>'res_raw_37118311'!$E$17</f>
-        <v/>
-      </c>
-      <c r="F83" s="11">
-        <f>'res_raw_37118311'!$F$17</f>
-        <v/>
-      </c>
-      <c r="G83" t="inlineStr"/>
-      <c r="H83" s="12">
-        <f>IFERROR(B83/$B$83*100,"")</f>
-        <v/>
-      </c>
-      <c r="I83" s="12">
-        <f>IFERROR(C83/$B$83*100,"")</f>
-        <v/>
-      </c>
-      <c r="J83" s="12">
-        <f>IFERROR(D83/$B$83*100,"")</f>
-        <v/>
-      </c>
-      <c r="K83" s="12">
-        <f>IFERROR(E83/$B$83*100,"")</f>
-        <v/>
-      </c>
-      <c r="L83" s="12">
-        <f>IFERROR(F83/$B$83*100,"")</f>
+          <t>Afkastningsgrad, %</t>
+        </is>
+      </c>
+      <c r="B83" s="13">
+        <f>IFERROR(($B$11+$B$13+$B$12)/$B$46*100,"")</f>
+        <v/>
+      </c>
+      <c r="C83" s="13">
+        <f>IFERROR(($C$11+$C$13+$C$12)/$C$46*100,"")</f>
+        <v/>
+      </c>
+      <c r="D83" s="13">
+        <f>IFERROR(($D$11+$D$13+$D$12)/$D$46*100,"")</f>
+        <v/>
+      </c>
+      <c r="E83" s="13">
+        <f>IFERROR(($E$11+$E$13+$E$12)/$E$46*100,"")</f>
+        <v/>
+      </c>
+      <c r="F83" s="13">
+        <f>IFERROR(($F$11+$F$13+$F$12)/$F$46*100,"")</f>
         <v/>
       </c>
     </row>
     <row r="84" ht="16" customHeight="1">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>Investering i materielle anlægsaktiver</t>
-        </is>
-      </c>
-      <c r="B84" s="5">
-        <f>'res_raw_37118311'!$B$18</f>
-        <v/>
-      </c>
-      <c r="C84" s="5">
-        <f>'res_raw_37118311'!$C$18</f>
-        <v/>
-      </c>
-      <c r="D84" s="5">
-        <f>'res_raw_37118311'!$D$18</f>
-        <v/>
-      </c>
-      <c r="E84" s="5">
-        <f>'res_raw_37118311'!$E$18</f>
-        <v/>
-      </c>
-      <c r="F84" s="5">
-        <f>'res_raw_37118311'!$F$18</f>
-        <v/>
-      </c>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" s="6">
-        <f>IFERROR(B84/$B$84*100,"")</f>
-        <v/>
-      </c>
-      <c r="I84" s="6">
-        <f>IFERROR(C84/$B$84*100,"")</f>
-        <v/>
-      </c>
-      <c r="J84" s="6">
-        <f>IFERROR(D84/$B$84*100,"")</f>
-        <v/>
-      </c>
-      <c r="K84" s="6">
-        <f>IFERROR(E84/$B$84*100,"")</f>
-        <v/>
-      </c>
-      <c r="L84" s="6">
-        <f>IFERROR(F84/$B$84*100,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="86" ht="22" customHeight="1">
-      <c r="A86" s="3" t="inlineStr">
-        <is>
-          <t>NØGLETAL</t>
-        </is>
-      </c>
-      <c r="B86" s="3" t="n">
-        <v>2020</v>
-      </c>
-      <c r="C86" s="3" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D86" s="3" t="n">
-        <v>2022</v>
-      </c>
-      <c r="E86" s="3" t="n">
-        <v>2023</v>
-      </c>
-      <c r="F86" s="3" t="n">
-        <v>2024</v>
+          <t>Overskudsgrad, %</t>
+        </is>
+      </c>
+      <c r="B84" s="14">
+        <f>IFERROR(($B$11+$B$13+$B$12)/$B$4*100,"")</f>
+        <v/>
+      </c>
+      <c r="C84" s="14">
+        <f>IFERROR(($C$11+$C$13+$C$12)/$C$4*100,"")</f>
+        <v/>
+      </c>
+      <c r="D84" s="14">
+        <f>IFERROR(($D$11+$D$13+$D$12)/$D$4*100,"")</f>
+        <v/>
+      </c>
+      <c r="E84" s="14">
+        <f>IFERROR(($E$11+$E$13+$E$12)/$E$4*100,"")</f>
+        <v/>
+      </c>
+      <c r="F84" s="14">
+        <f>IFERROR(($F$11+$F$13+$F$12)/$F$4*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85" ht="16" customHeight="1">
+      <c r="A85" s="10" t="inlineStr">
+        <is>
+          <t>Aktivernes omsætningshastighed, gange</t>
+        </is>
+      </c>
+      <c r="B85" s="13">
+        <f>IFERROR($B$4/$B$46,"")</f>
+        <v/>
+      </c>
+      <c r="C85" s="13">
+        <f>IFERROR($C$4/$C$46,"")</f>
+        <v/>
+      </c>
+      <c r="D85" s="13">
+        <f>IFERROR($D$4/$D$46,"")</f>
+        <v/>
+      </c>
+      <c r="E85" s="13">
+        <f>IFERROR($E$4/$E$46,"")</f>
+        <v/>
+      </c>
+      <c r="F85" s="13">
+        <f>IFERROR($F$4/$F$46,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86" ht="16" customHeight="1">
+      <c r="A86" s="4" t="inlineStr">
+        <is>
+          <t>Egenkapitalens forrentning, %</t>
+        </is>
+      </c>
+      <c r="B86" s="14">
+        <f>IFERROR($B$16/$B$55*100,"")</f>
+        <v/>
+      </c>
+      <c r="C86" s="14">
+        <f>IFERROR($C$16/$C$55*100,"")</f>
+        <v/>
+      </c>
+      <c r="D86" s="14">
+        <f>IFERROR($D$16/$D$55*100,"")</f>
+        <v/>
+      </c>
+      <c r="E86" s="14">
+        <f>IFERROR($E$16/$E$55*100,"")</f>
+        <v/>
+      </c>
+      <c r="F86" s="14">
+        <f>IFERROR($F$16/$F$55*100,"")</f>
+        <v/>
       </c>
     </row>
     <row r="87" ht="16" customHeight="1">
       <c r="A87" s="10" t="inlineStr">
         <is>
-          <t>Afkastningsgrad, %</t>
+          <t>Gældsrente, %</t>
         </is>
       </c>
       <c r="B87" s="13">
-        <f>IFERROR(($B$11+$B$13+$B$12)/$B$50*100,"")</f>
+        <f>IFERROR($B$14/($B$76-$B$55)*100,"")</f>
         <v/>
       </c>
       <c r="C87" s="13">
-        <f>IFERROR(($C$11+$C$13+$C$12)/$C$50*100,"")</f>
+        <f>IFERROR($C$14/($C$76-$C$55)*100,"")</f>
         <v/>
       </c>
       <c r="D87" s="13">
-        <f>IFERROR(($D$11+$D$13+$D$12)/$D$50*100,"")</f>
+        <f>IFERROR($D$14/($D$76-$D$55)*100,"")</f>
         <v/>
       </c>
       <c r="E87" s="13">
-        <f>IFERROR(($E$11+$E$13+$E$12)/$E$50*100,"")</f>
+        <f>IFERROR($E$14/($E$76-$E$55)*100,"")</f>
         <v/>
       </c>
       <c r="F87" s="13">
-        <f>IFERROR(($F$11+$F$13+$F$12)/$F$50*100,"")</f>
+        <f>IFERROR($F$14/($F$76-$F$55)*100,"")</f>
         <v/>
       </c>
     </row>
     <row r="88" ht="16" customHeight="1">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>Overskudsgrad, %</t>
+          <t>Soliditetsgrad, %</t>
         </is>
       </c>
       <c r="B88" s="14">
-        <f>IFERROR(($B$11+$B$13+$B$12)/$B$4*100,"")</f>
+        <f>IFERROR($B$55/$B$46*100,"")</f>
         <v/>
       </c>
       <c r="C88" s="14">
-        <f>IFERROR(($C$11+$C$13+$C$12)/$C$4*100,"")</f>
+        <f>IFERROR($C$55/$C$46*100,"")</f>
         <v/>
       </c>
       <c r="D88" s="14">
-        <f>IFERROR(($D$11+$D$13+$D$12)/$D$4*100,"")</f>
+        <f>IFERROR($D$55/$D$46*100,"")</f>
         <v/>
       </c>
       <c r="E88" s="14">
-        <f>IFERROR(($E$11+$E$13+$E$12)/$E$4*100,"")</f>
+        <f>IFERROR($E$55/$E$46*100,"")</f>
         <v/>
       </c>
       <c r="F88" s="14">
-        <f>IFERROR(($F$11+$F$13+$F$12)/$F$4*100,"")</f>
+        <f>IFERROR($F$55/$F$46*100,"")</f>
         <v/>
       </c>
     </row>
     <row r="89" ht="16" customHeight="1">
       <c r="A89" s="10" t="inlineStr">
         <is>
-          <t>Aktivernes omsætningshastighed, gange</t>
+          <t>Gearing</t>
         </is>
       </c>
       <c r="B89" s="13">
-        <f>IFERROR($B$4/$B$50,"")</f>
+        <f>IFERROR(($B$76-$B$55)/$B$55,"")</f>
         <v/>
       </c>
       <c r="C89" s="13">
-        <f>IFERROR($C$4/$C$50,"")</f>
+        <f>IFERROR(($C$76-$C$55)/$C$55,"")</f>
         <v/>
       </c>
       <c r="D89" s="13">
-        <f>IFERROR($D$4/$D$50,"")</f>
+        <f>IFERROR(($D$76-$D$55)/$D$55,"")</f>
         <v/>
       </c>
       <c r="E89" s="13">
-        <f>IFERROR($E$4/$E$50,"")</f>
+        <f>IFERROR(($E$76-$E$55)/$E$55,"")</f>
         <v/>
       </c>
       <c r="F89" s="13">
-        <f>IFERROR($F$4/$F$50,"")</f>
+        <f>IFERROR(($F$76-$F$55)/$F$55,"")</f>
         <v/>
       </c>
     </row>
     <row r="90" ht="16" customHeight="1">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>Egenkapitalens forrentning, %</t>
+          <t>Likviditetsgrad, %</t>
         </is>
       </c>
       <c r="B90" s="14">
-        <f>IFERROR($B$16/$B$59*100,"")</f>
+        <f>IFERROR($B$45/$B$74*100,"")</f>
         <v/>
       </c>
       <c r="C90" s="14">
-        <f>IFERROR($C$16/$C$59*100,"")</f>
+        <f>IFERROR($C$45/$C$74*100,"")</f>
         <v/>
       </c>
       <c r="D90" s="14">
-        <f>IFERROR($D$16/$D$59*100,"")</f>
+        <f>IFERROR($D$45/$D$74*100,"")</f>
         <v/>
       </c>
       <c r="E90" s="14">
-        <f>IFERROR($E$16/$E$59*100,"")</f>
+        <f>IFERROR($E$45/$E$74*100,"")</f>
         <v/>
       </c>
       <c r="F90" s="14">
-        <f>IFERROR($F$16/$F$59*100,"")</f>
+        <f>IFERROR($F$45/$F$74*100,"")</f>
         <v/>
       </c>
     </row>
     <row r="91" ht="16" customHeight="1">
       <c r="A91" s="10" t="inlineStr">
         <is>
-          <t>Gældsrente, %</t>
+          <t>Rentemarginal, %</t>
         </is>
       </c>
       <c r="B91" s="13">
-        <f>IFERROR($B$14/($B$80-$B$59)*100,"")</f>
+        <f>IFERROR(B83-B87,"")</f>
         <v/>
       </c>
       <c r="C91" s="13">
-        <f>IFERROR($C$14/($C$80-$C$59)*100,"")</f>
+        <f>IFERROR(C83-C87,"")</f>
         <v/>
       </c>
       <c r="D91" s="13">
-        <f>IFERROR($D$14/($D$80-$D$59)*100,"")</f>
+        <f>IFERROR(D83-D87,"")</f>
         <v/>
       </c>
       <c r="E91" s="13">
-        <f>IFERROR($E$14/($E$80-$E$59)*100,"")</f>
+        <f>IFERROR(E83-E87,"")</f>
         <v/>
       </c>
       <c r="F91" s="13">
-        <f>IFERROR($F$14/($F$80-$F$59)*100,"")</f>
+        <f>IFERROR(F83-F87,"")</f>
         <v/>
       </c>
     </row>
     <row r="92" ht="16" customHeight="1">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>Soliditetsgrad, %</t>
+          <t>Gældsandel, %</t>
         </is>
       </c>
       <c r="B92" s="14">
-        <f>IFERROR($B$59/$B$50*100,"")</f>
+        <f>IFERROR(($B$76-$B$55)/$B$46*100,"")</f>
         <v/>
       </c>
       <c r="C92" s="14">
-        <f>IFERROR($C$59/$C$50*100,"")</f>
+        <f>IFERROR(($C$76-$C$55)/$C$46*100,"")</f>
         <v/>
       </c>
       <c r="D92" s="14">
-        <f>IFERROR($D$59/$D$50*100,"")</f>
+        <f>IFERROR(($D$76-$D$55)/$D$46*100,"")</f>
         <v/>
       </c>
       <c r="E92" s="14">
-        <f>IFERROR($E$59/$E$50*100,"")</f>
+        <f>IFERROR(($E$76-$E$55)/$E$46*100,"")</f>
         <v/>
       </c>
       <c r="F92" s="14">
-        <f>IFERROR($F$59/$F$50*100,"")</f>
+        <f>IFERROR(($F$76-$F$55)/$F$46*100,"")</f>
         <v/>
       </c>
     </row>
     <row r="93" ht="16" customHeight="1">
       <c r="A93" s="10" t="inlineStr">
         <is>
-          <t>Gearing</t>
+          <t>Kapitalbindingsgrad, %</t>
         </is>
       </c>
       <c r="B93" s="13">
-        <f>IFERROR(($B$80-$B$59)/$B$59,"")</f>
+        <f>IFERROR($B$30/($B$55+$B$62)*100,"")</f>
         <v/>
       </c>
       <c r="C93" s="13">
-        <f>IFERROR(($C$80-$C$59)/$C$59,"")</f>
+        <f>IFERROR($C$30/($C$55+$C$62)*100,"")</f>
         <v/>
       </c>
       <c r="D93" s="13">
-        <f>IFERROR(($D$80-$D$59)/$D$59,"")</f>
+        <f>IFERROR($D$30/($D$55+$D$62)*100,"")</f>
         <v/>
       </c>
       <c r="E93" s="13">
-        <f>IFERROR(($E$80-$E$59)/$E$59,"")</f>
+        <f>IFERROR($E$30/($E$55+$E$62)*100,"")</f>
         <v/>
       </c>
       <c r="F93" s="13">
-        <f>IFERROR(($F$80-$F$59)/$F$59,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="94" ht="16" customHeight="1">
-      <c r="A94" s="4" t="inlineStr">
-        <is>
-          <t>Likviditetsgrad, %</t>
-        </is>
-      </c>
-      <c r="B94" s="14">
-        <f>IFERROR($B$49/$B$78*100,"")</f>
-        <v/>
-      </c>
-      <c r="C94" s="14">
-        <f>IFERROR($C$49/$C$78*100,"")</f>
-        <v/>
-      </c>
-      <c r="D94" s="14">
-        <f>IFERROR($D$49/$D$78*100,"")</f>
-        <v/>
-      </c>
-      <c r="E94" s="14">
-        <f>IFERROR($E$49/$E$78*100,"")</f>
-        <v/>
-      </c>
-      <c r="F94" s="14">
-        <f>IFERROR($F$49/$F$78*100,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="95" ht="16" customHeight="1">
-      <c r="A95" s="10" t="inlineStr">
-        <is>
-          <t>Rentemarginal, %</t>
-        </is>
-      </c>
-      <c r="B95" s="13">
-        <f>IFERROR(B87-B91,"")</f>
-        <v/>
-      </c>
-      <c r="C95" s="13">
-        <f>IFERROR(C87-C91,"")</f>
-        <v/>
-      </c>
-      <c r="D95" s="13">
-        <f>IFERROR(D87-D91,"")</f>
-        <v/>
-      </c>
-      <c r="E95" s="13">
-        <f>IFERROR(E87-E91,"")</f>
-        <v/>
-      </c>
-      <c r="F95" s="13">
-        <f>IFERROR(F87-F91,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="96" ht="16" customHeight="1">
-      <c r="A96" s="4" t="inlineStr">
-        <is>
-          <t>Gældsandel, %</t>
-        </is>
-      </c>
-      <c r="B96" s="14">
-        <f>IFERROR(($B$80-$B$59)/$B$50*100,"")</f>
-        <v/>
-      </c>
-      <c r="C96" s="14">
-        <f>IFERROR(($C$80-$C$59)/$C$50*100,"")</f>
-        <v/>
-      </c>
-      <c r="D96" s="14">
-        <f>IFERROR(($D$80-$D$59)/$D$50*100,"")</f>
-        <v/>
-      </c>
-      <c r="E96" s="14">
-        <f>IFERROR(($E$80-$E$59)/$E$50*100,"")</f>
-        <v/>
-      </c>
-      <c r="F96" s="14">
-        <f>IFERROR(($F$80-$F$59)/$F$50*100,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="97" ht="16" customHeight="1">
-      <c r="A97" s="10" t="inlineStr">
-        <is>
-          <t>Kapitalbindingsgrad, %</t>
-        </is>
-      </c>
-      <c r="B97" s="13">
-        <f>IFERROR($B$34/($B$59+$B$66)*100,"")</f>
-        <v/>
-      </c>
-      <c r="C97" s="13">
-        <f>IFERROR($C$34/($C$59+$C$66)*100,"")</f>
-        <v/>
-      </c>
-      <c r="D97" s="13">
-        <f>IFERROR($D$34/($D$59+$D$66)*100,"")</f>
-        <v/>
-      </c>
-      <c r="E97" s="13">
-        <f>IFERROR($E$34/($E$59+$E$66)*100,"")</f>
-        <v/>
-      </c>
-      <c r="F97" s="13">
-        <f>IFERROR($F$34/($F$59+$F$66)*100,"")</f>
-        <v/>
+        <f>IFERROR($F$30/($F$55+$F$62)*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="15" t="inlineStr">
+        <is>
+          <t>Pengestrømsopgørelse ikke offentliggjort (jf. koncernfritagelse, ÅRL §86, stk. 4)</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -4721,19 +4536,19 @@
         </is>
       </c>
       <c r="B1" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C1" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D1" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E1" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F1" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="2">
@@ -4743,19 +4558,19 @@
         </is>
       </c>
       <c r="B2" s="16" t="n">
-        <v>189928</v>
+        <v>238338</v>
       </c>
       <c r="C2" s="16" t="n">
-        <v>238338</v>
+        <v>182756</v>
       </c>
       <c r="D2" s="16" t="n">
-        <v>182756</v>
+        <v>190302</v>
       </c>
       <c r="E2" s="16" t="n">
-        <v>190302</v>
+        <v>163922</v>
       </c>
       <c r="F2" s="16" t="n">
-        <v>163922</v>
+        <v>129834</v>
       </c>
     </row>
     <row r="3">
@@ -4765,19 +4580,19 @@
         </is>
       </c>
       <c r="B3" s="16" t="n">
-        <v>162195</v>
+        <v>209902</v>
       </c>
       <c r="C3" s="16" t="n">
-        <v>209902</v>
+        <v>180826</v>
       </c>
       <c r="D3" s="16" t="n">
-        <v>180826</v>
+        <v>175855</v>
       </c>
       <c r="E3" s="16" t="n">
-        <v>175855</v>
+        <v>150316</v>
       </c>
       <c r="F3" s="16" t="n">
-        <v>150316</v>
+        <v>125386</v>
       </c>
     </row>
     <row r="4">
@@ -4787,19 +4602,19 @@
         </is>
       </c>
       <c r="B4" s="16" t="n">
-        <v>27733</v>
+        <v>28436</v>
       </c>
       <c r="C4" s="16" t="n">
-        <v>28436</v>
+        <v>1930</v>
       </c>
       <c r="D4" s="16" t="n">
-        <v>1930</v>
+        <v>14447</v>
       </c>
       <c r="E4" s="16" t="n">
-        <v>14447</v>
+        <v>13607</v>
       </c>
       <c r="F4" s="16" t="n">
-        <v>13607</v>
+        <v>4448</v>
       </c>
     </row>
     <row r="5">
@@ -4809,19 +4624,19 @@
         </is>
       </c>
       <c r="B5" s="16" t="n">
-        <v>23581</v>
+        <v>30165</v>
       </c>
       <c r="C5" s="16" t="n">
-        <v>30165</v>
+        <v>20424</v>
       </c>
       <c r="D5" s="16" t="n">
-        <v>20424</v>
+        <v>26816</v>
       </c>
       <c r="E5" s="16" t="n">
-        <v>26816</v>
+        <v>21280</v>
       </c>
       <c r="F5" s="16" t="n">
-        <v>21280</v>
+        <v>21442</v>
       </c>
     </row>
     <row r="6">
@@ -4831,19 +4646,19 @@
         </is>
       </c>
       <c r="B6" s="16" t="n">
-        <v>7007</v>
+        <v>8476</v>
       </c>
       <c r="C6" s="16" t="n">
-        <v>8476</v>
+        <v>18141</v>
       </c>
       <c r="D6" s="16" t="n">
-        <v>18141</v>
+        <v>18592</v>
       </c>
       <c r="E6" s="16" t="n">
-        <v>18592</v>
+        <v>17160</v>
       </c>
       <c r="F6" s="16" t="n">
-        <v>17160</v>
+        <v>20842</v>
       </c>
     </row>
     <row r="7">
@@ -4852,19 +4667,19 @@
           <t>Andre driftsindtægter</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n"/>
+      <c r="B7" s="16" t="n">
+        <v>508</v>
+      </c>
       <c r="C7" s="16" t="n">
-        <v>508</v>
+        <v>850</v>
       </c>
       <c r="D7" s="16" t="n">
-        <v>850</v>
+        <v>1668</v>
       </c>
       <c r="E7" s="16" t="n">
-        <v>1668</v>
-      </c>
-      <c r="F7" s="16" t="n">
         <v>0</v>
       </c>
+      <c r="F7" s="16" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
@@ -4873,14 +4688,12 @@
         </is>
       </c>
       <c r="B8" s="16" t="n">
-        <v>1527</v>
+        <v>932</v>
       </c>
       <c r="C8" s="16" t="n">
-        <v>932</v>
-      </c>
-      <c r="D8" s="16" t="n">
         <v>0</v>
       </c>
+      <c r="D8" s="16" t="n"/>
       <c r="E8" s="16" t="n"/>
       <c r="F8" s="16" t="n"/>
     </row>
@@ -4891,19 +4704,19 @@
         </is>
       </c>
       <c r="B9" s="16" t="n">
-        <v>-4382</v>
+        <v>-10629</v>
       </c>
       <c r="C9" s="16" t="n">
-        <v>-10629</v>
+        <v>-35785</v>
       </c>
       <c r="D9" s="16" t="n">
-        <v>-35785</v>
+        <v>-29293</v>
       </c>
       <c r="E9" s="16" t="n">
-        <v>-29293</v>
+        <v>-24833</v>
       </c>
       <c r="F9" s="16" t="n">
-        <v>-24833</v>
+        <v>-37837</v>
       </c>
     </row>
     <row r="10">
@@ -4913,20 +4726,18 @@
         </is>
       </c>
       <c r="B10" s="16" t="n">
-        <v>-58</v>
+        <v>-47</v>
       </c>
       <c r="C10" s="16" t="n">
-        <v>-47</v>
+        <v>41</v>
       </c>
       <c r="D10" s="16" t="n">
-        <v>41</v>
+        <v>177</v>
       </c>
       <c r="E10" s="16" t="n">
-        <v>177</v>
-      </c>
-      <c r="F10" s="16" t="n">
         <v>0</v>
       </c>
+      <c r="F10" s="16" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
@@ -4935,19 +4746,19 @@
         </is>
       </c>
       <c r="B11" s="16" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C11" s="16" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D11" s="16" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E11" s="16" t="n">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="F11" s="16" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12">
@@ -4956,18 +4767,20 @@
           <t>Finansielle omkostninger</t>
         </is>
       </c>
-      <c r="B12" s="16" t="n"/>
+      <c r="B12" s="16" t="n">
+        <v>5776</v>
+      </c>
       <c r="C12" s="16" t="n">
-        <v>5776</v>
+        <v>5838</v>
       </c>
       <c r="D12" s="16" t="n">
-        <v>5838</v>
+        <v>14089</v>
       </c>
       <c r="E12" s="16" t="n">
-        <v>14089</v>
+        <v>13242</v>
       </c>
       <c r="F12" s="16" t="n">
-        <v>13242</v>
+        <v>7068</v>
       </c>
     </row>
     <row r="13">
@@ -4976,13 +4789,13 @@
           <t>Finansielle poster, netto</t>
         </is>
       </c>
-      <c r="B13" s="16" t="n"/>
+      <c r="B13" s="16" t="n">
+        <v>-5751</v>
+      </c>
       <c r="C13" s="16" t="n">
-        <v>-5751</v>
-      </c>
-      <c r="D13" s="16" t="n">
         <v>-5824</v>
       </c>
+      <c r="D13" s="16" t="n"/>
       <c r="E13" s="16" t="n"/>
       <c r="F13" s="16" t="n"/>
     </row>
@@ -4993,19 +4806,19 @@
         </is>
       </c>
       <c r="B14" s="16" t="n">
-        <v>-7082</v>
+        <v>-16427</v>
       </c>
       <c r="C14" s="16" t="n">
-        <v>-16427</v>
+        <v>-41568</v>
       </c>
       <c r="D14" s="16" t="n">
-        <v>-41568</v>
+        <v>-43196</v>
       </c>
       <c r="E14" s="16" t="n">
-        <v>-43196</v>
+        <v>-38045</v>
       </c>
       <c r="F14" s="16" t="n">
-        <v>-38045</v>
+        <v>-44874</v>
       </c>
     </row>
     <row r="15">
@@ -5015,16 +4828,16 @@
         </is>
       </c>
       <c r="B15" s="16" t="n">
-        <v>-1540</v>
+        <v>-3565</v>
       </c>
       <c r="C15" s="16" t="n">
-        <v>-3565</v>
+        <v>-9109</v>
       </c>
       <c r="D15" s="16" t="n">
-        <v>-9109</v>
+        <v>3018</v>
       </c>
       <c r="E15" s="16" t="n">
-        <v>3018</v>
+        <v>0</v>
       </c>
       <c r="F15" s="16" t="n">
         <v>0</v>
@@ -5037,19 +4850,19 @@
         </is>
       </c>
       <c r="B16" s="16" t="n">
-        <v>-5542</v>
+        <v>-12862</v>
       </c>
       <c r="C16" s="16" t="n">
-        <v>-12862</v>
+        <v>-32459</v>
       </c>
       <c r="D16" s="16" t="n">
-        <v>-32459</v>
+        <v>-46214</v>
       </c>
       <c r="E16" s="16" t="n">
-        <v>-46214</v>
+        <v>-38045</v>
       </c>
       <c r="F16" s="16" t="n">
-        <v>-38045</v>
+        <v>-44874</v>
       </c>
     </row>
     <row r="17">
@@ -5059,19 +4872,19 @@
         </is>
       </c>
       <c r="B17" s="16" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C17" s="16" t="n">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="D17" s="16" t="n">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="E17" s="16" t="n">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="F17" s="16" t="n">
-        <v>96</v>
+        <v>83</v>
       </c>
     </row>
     <row r="18">
@@ -5081,14 +4894,12 @@
         </is>
       </c>
       <c r="B18" s="16" t="n">
-        <v>4855</v>
+        <v>4557</v>
       </c>
       <c r="C18" s="16" t="n">
-        <v>4557</v>
-      </c>
-      <c r="D18" s="16" t="n">
         <v>18071</v>
       </c>
+      <c r="D18" s="16" t="n"/>
       <c r="E18" s="16" t="n"/>
       <c r="F18" s="16" t="n"/>
     </row>
@@ -5103,7 +4914,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F59"/>
+  <dimension ref="A1:F55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="72" customWidth="1" min="1" max="1"/>
@@ -5121,68 +4932,94 @@
         </is>
       </c>
       <c r="B1" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C1" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D1" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E1" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F1" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="15" t="inlineStr">
         <is>
-          <t>Udviklingsprojekter</t>
+          <t>Grunde og bygninger</t>
         </is>
       </c>
       <c r="B2" s="16" t="n">
-        <v>184</v>
-      </c>
-      <c r="C2" s="16" t="n"/>
-      <c r="D2" s="16" t="n"/>
-      <c r="E2" s="16" t="n"/>
-      <c r="F2" s="16" t="n"/>
+        <v>56379</v>
+      </c>
+      <c r="C2" s="16" t="n">
+        <v>54228</v>
+      </c>
+      <c r="D2" s="16" t="n">
+        <v>53778</v>
+      </c>
+      <c r="E2" s="16" t="n">
+        <v>51508</v>
+      </c>
+      <c r="F2" s="16" t="n">
+        <v>49135</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="15" t="inlineStr">
         <is>
-          <t>Patenter, varemærker mv.</t>
-        </is>
-      </c>
-      <c r="B3" s="16" t="n"/>
-      <c r="C3" s="16" t="n"/>
-      <c r="D3" s="16" t="n"/>
-      <c r="E3" s="16" t="n"/>
-      <c r="F3" s="16" t="n"/>
+          <t>Produktionsanlæg og maskiner</t>
+        </is>
+      </c>
+      <c r="B3" s="16" t="n">
+        <v>57314</v>
+      </c>
+      <c r="C3" s="16" t="n">
+        <v>53850</v>
+      </c>
+      <c r="D3" s="16" t="n">
+        <v>64917</v>
+      </c>
+      <c r="E3" s="16" t="n">
+        <v>59779</v>
+      </c>
+      <c r="F3" s="16" t="n">
+        <v>75285</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="15" t="inlineStr">
         <is>
-          <t>Goodwill</t>
-        </is>
-      </c>
-      <c r="B4" s="16" t="n"/>
-      <c r="C4" s="16" t="n"/>
-      <c r="D4" s="16" t="n"/>
-      <c r="E4" s="16" t="n"/>
-      <c r="F4" s="16" t="n"/>
+          <t>Driftsmateriel og inventar</t>
+        </is>
+      </c>
+      <c r="B4" s="16" t="n">
+        <v>467</v>
+      </c>
+      <c r="C4" s="16" t="n">
+        <v>408</v>
+      </c>
+      <c r="D4" s="16" t="n">
+        <v>308</v>
+      </c>
+      <c r="E4" s="16" t="n">
+        <v>2202</v>
+      </c>
+      <c r="F4" s="16" t="n">
+        <v>1197</v>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="inlineStr">
-        <is>
-          <t>Immaterielle anlægsaktiver</t>
-        </is>
-      </c>
-      <c r="B5" s="16" t="n">
-        <v>184</v>
-      </c>
+      <c r="A5" s="15" t="inlineStr">
+        <is>
+          <t>Indretning af lejede lokaler</t>
+        </is>
+      </c>
+      <c r="B5" s="16" t="n"/>
       <c r="C5" s="16" t="n"/>
       <c r="D5" s="16" t="n"/>
       <c r="E5" s="16" t="n"/>
@@ -5191,73 +5028,71 @@
     <row r="6">
       <c r="A6" s="15" t="inlineStr">
         <is>
-          <t>Grunde og bygninger</t>
+          <t>Forudbetaling og anlægsaktiver under opførelse</t>
         </is>
       </c>
       <c r="B6" s="16" t="n">
-        <v>59006</v>
+        <v>888</v>
       </c>
       <c r="C6" s="16" t="n">
-        <v>56379</v>
+        <v>0</v>
       </c>
       <c r="D6" s="16" t="n">
-        <v>54228</v>
+        <v>6837</v>
       </c>
       <c r="E6" s="16" t="n">
-        <v>53778</v>
+        <v>23330</v>
       </c>
       <c r="F6" s="16" t="n">
-        <v>51508</v>
+        <v>218</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
-        <is>
-          <t>Produktionsanlæg og maskiner</t>
+      <c r="A7" s="17" t="inlineStr">
+        <is>
+          <t>Materielle anlægsaktiver</t>
         </is>
       </c>
       <c r="B7" s="16" t="n">
-        <v>66135</v>
+        <v>116323</v>
       </c>
       <c r="C7" s="16" t="n">
-        <v>57314</v>
+        <v>125132</v>
       </c>
       <c r="D7" s="16" t="n">
-        <v>53850</v>
+        <v>125840</v>
       </c>
       <c r="E7" s="16" t="n">
-        <v>64917</v>
+        <v>136819</v>
       </c>
       <c r="F7" s="16" t="n">
-        <v>59779</v>
+        <v>125834</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>Driftsmateriel og inventar</t>
+          <t>Kapitalandele, dattervirksomheder</t>
         </is>
       </c>
       <c r="B8" s="16" t="n">
-        <v>601</v>
+        <v>3612</v>
       </c>
       <c r="C8" s="16" t="n">
-        <v>467</v>
+        <v>3653</v>
       </c>
       <c r="D8" s="16" t="n">
-        <v>408</v>
+        <v>3836</v>
       </c>
       <c r="E8" s="16" t="n">
-        <v>308</v>
-      </c>
-      <c r="F8" s="16" t="n">
-        <v>2202</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F8" s="16" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>Indretning af lejede lokaler</t>
+          <t>Deposita</t>
         </is>
       </c>
       <c r="B9" s="16" t="n"/>
@@ -5267,650 +5102,632 @@
       <c r="F9" s="16" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
-        <is>
-          <t>Forudbetaling og anlægsaktiver under opførelse</t>
+      <c r="A10" s="17" t="inlineStr">
+        <is>
+          <t>Finansielle anlægsaktiver</t>
         </is>
       </c>
       <c r="B10" s="16" t="n">
-        <v>0</v>
+        <v>3658</v>
       </c>
       <c r="C10" s="16" t="n">
-        <v>888</v>
+        <v>3698</v>
       </c>
       <c r="D10" s="16" t="n">
-        <v>0</v>
+        <v>3874</v>
       </c>
       <c r="E10" s="16" t="n">
-        <v>6837</v>
+        <v>47</v>
       </c>
       <c r="F10" s="16" t="n">
-        <v>23330</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="17" t="inlineStr">
         <is>
-          <t>Materielle anlægsaktiver</t>
+          <t>Anlægsaktiver</t>
         </is>
       </c>
       <c r="B11" s="16" t="n">
-        <v>125742</v>
+        <v>119981</v>
       </c>
       <c r="C11" s="16" t="n">
-        <v>116323</v>
+        <v>128830</v>
       </c>
       <c r="D11" s="16" t="n">
-        <v>125132</v>
+        <v>129714</v>
       </c>
       <c r="E11" s="16" t="n">
-        <v>125840</v>
+        <v>136865</v>
       </c>
       <c r="F11" s="16" t="n">
-        <v>136819</v>
+        <v>125875</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>Kapitalandele, dattervirksomheder</t>
+          <t>Råvarer og hjælpematerialer</t>
         </is>
       </c>
       <c r="B12" s="16" t="n">
-        <v>3659</v>
+        <v>12037</v>
       </c>
       <c r="C12" s="16" t="n">
-        <v>3612</v>
+        <v>15830</v>
       </c>
       <c r="D12" s="16" t="n">
-        <v>3653</v>
+        <v>22819</v>
       </c>
       <c r="E12" s="16" t="n">
-        <v>3836</v>
+        <v>13798</v>
       </c>
       <c r="F12" s="16" t="n">
-        <v>0</v>
+        <v>13534</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>Deposita</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="n"/>
-      <c r="C13" s="16" t="n"/>
-      <c r="D13" s="16" t="n"/>
-      <c r="E13" s="16" t="n"/>
-      <c r="F13" s="16" t="n"/>
+          <t>Varer under fremstilling</t>
+        </is>
+      </c>
+      <c r="B13" s="16" t="n">
+        <v>2682</v>
+      </c>
+      <c r="C13" s="16" t="n">
+        <v>3230</v>
+      </c>
+      <c r="D13" s="16" t="n">
+        <v>2975</v>
+      </c>
+      <c r="E13" s="16" t="n">
+        <v>1701</v>
+      </c>
+      <c r="F13" s="16" t="n">
+        <v>1590</v>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="17" t="inlineStr">
-        <is>
-          <t>Finansielle anlægsaktiver</t>
+      <c r="A14" s="15" t="inlineStr">
+        <is>
+          <t>Færdigvarer og handelsvarer</t>
         </is>
       </c>
       <c r="B14" s="16" t="n">
-        <v>41</v>
+        <v>25677</v>
       </c>
       <c r="C14" s="16" t="n">
-        <v>3658</v>
+        <v>29245</v>
       </c>
       <c r="D14" s="16" t="n">
-        <v>3698</v>
+        <v>14310</v>
       </c>
       <c r="E14" s="16" t="n">
-        <v>3874</v>
+        <v>8747</v>
       </c>
       <c r="F14" s="16" t="n">
-        <v>47</v>
+        <v>4188</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="17" t="inlineStr">
         <is>
-          <t>Anlægsaktiver</t>
+          <t>Varebeholdninger</t>
         </is>
       </c>
       <c r="B15" s="16" t="n">
-        <v>125967</v>
+        <v>40396</v>
       </c>
       <c r="C15" s="16" t="n">
-        <v>119981</v>
+        <v>48306</v>
       </c>
       <c r="D15" s="16" t="n">
-        <v>128830</v>
+        <v>40104</v>
       </c>
       <c r="E15" s="16" t="n">
-        <v>129714</v>
+        <v>24246</v>
       </c>
       <c r="F15" s="16" t="n">
-        <v>136865</v>
+        <v>19312</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>Råvarer og hjælpematerialer</t>
+          <t>Tilgodehavender fra salg og tjenesteydelser</t>
         </is>
       </c>
       <c r="B16" s="16" t="n">
-        <v>13900</v>
+        <v>16141</v>
       </c>
       <c r="C16" s="16" t="n">
-        <v>12037</v>
+        <v>22336</v>
       </c>
       <c r="D16" s="16" t="n">
-        <v>15830</v>
+        <v>16655</v>
       </c>
       <c r="E16" s="16" t="n">
-        <v>22819</v>
+        <v>10787</v>
       </c>
       <c r="F16" s="16" t="n">
-        <v>13798</v>
+        <v>13474</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>Varer under fremstilling</t>
+          <t>Tilgodehavender hos tilknyttede virksomheder</t>
         </is>
       </c>
       <c r="B17" s="16" t="n">
-        <v>1856</v>
+        <v>144</v>
       </c>
       <c r="C17" s="16" t="n">
-        <v>2682</v>
+        <v>1189</v>
       </c>
       <c r="D17" s="16" t="n">
-        <v>3230</v>
+        <v>0</v>
       </c>
       <c r="E17" s="16" t="n">
-        <v>2975</v>
+        <v>51</v>
       </c>
       <c r="F17" s="16" t="n">
-        <v>1701</v>
+        <v>453</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>Færdigvarer og handelsvarer</t>
+          <t>Andre tilgodehavender</t>
         </is>
       </c>
       <c r="B18" s="16" t="n">
-        <v>18715</v>
+        <v>4106</v>
       </c>
       <c r="C18" s="16" t="n">
-        <v>25677</v>
+        <v>1514</v>
       </c>
       <c r="D18" s="16" t="n">
-        <v>29245</v>
+        <v>584</v>
       </c>
       <c r="E18" s="16" t="n">
-        <v>14310</v>
+        <v>3271</v>
       </c>
       <c r="F18" s="16" t="n">
-        <v>8747</v>
+        <v>2224</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="17" t="inlineStr">
-        <is>
-          <t>Varebeholdninger</t>
+      <c r="A19" s="15" t="inlineStr">
+        <is>
+          <t>Periodeafgrænsningsposter (aktiver)</t>
         </is>
       </c>
       <c r="B19" s="16" t="n">
-        <v>34471</v>
+        <v>2507</v>
       </c>
       <c r="C19" s="16" t="n">
-        <v>40396</v>
+        <v>2651</v>
       </c>
       <c r="D19" s="16" t="n">
-        <v>48306</v>
+        <v>2062</v>
       </c>
       <c r="E19" s="16" t="n">
-        <v>40104</v>
+        <v>1549</v>
       </c>
       <c r="F19" s="16" t="n">
-        <v>24246</v>
+        <v>1804</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t>Tilgodehavender fra salg og tjenesteydelser</t>
+          <t>Udskudt skatteaktiv</t>
         </is>
       </c>
       <c r="B20" s="16" t="n">
-        <v>24910</v>
+        <v>0</v>
       </c>
       <c r="C20" s="16" t="n">
-        <v>16141</v>
+        <v>3048</v>
       </c>
       <c r="D20" s="16" t="n">
-        <v>22336</v>
+        <v>0</v>
       </c>
       <c r="E20" s="16" t="n">
-        <v>16655</v>
+        <v>0</v>
       </c>
       <c r="F20" s="16" t="n">
-        <v>10787</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>Tilgodehavender hos tilknyttede virksomheder</t>
+          <t>Tilgodehavende skat hos tilknyttede virksomheder</t>
         </is>
       </c>
       <c r="B21" s="16" t="n"/>
-      <c r="C21" s="16" t="n">
-        <v>144</v>
-      </c>
-      <c r="D21" s="16" t="n">
-        <v>1189</v>
-      </c>
-      <c r="E21" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" s="16" t="n">
-        <v>51</v>
-      </c>
+      <c r="C21" s="16" t="n"/>
+      <c r="D21" s="16" t="n"/>
+      <c r="E21" s="16" t="n"/>
+      <c r="F21" s="16" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>Andre tilgodehavender</t>
+          <t>Kortfristede skattetilgodehavender</t>
         </is>
       </c>
       <c r="B22" s="16" t="n">
-        <v>1398</v>
+        <v>11</v>
       </c>
       <c r="C22" s="16" t="n">
-        <v>4106</v>
+        <v>10</v>
       </c>
       <c r="D22" s="16" t="n">
-        <v>1514</v>
+        <v>2</v>
       </c>
       <c r="E22" s="16" t="n">
-        <v>584</v>
+        <v>5</v>
       </c>
       <c r="F22" s="16" t="n">
-        <v>3271</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="15" t="inlineStr">
-        <is>
-          <t>Periodeafgrænsningsposter (aktiver)</t>
+      <c r="A23" s="17" t="inlineStr">
+        <is>
+          <t>Tilgodehavender</t>
         </is>
       </c>
       <c r="B23" s="16" t="n">
-        <v>1188</v>
+        <v>22909</v>
       </c>
       <c r="C23" s="16" t="n">
-        <v>2507</v>
+        <v>30748</v>
       </c>
       <c r="D23" s="16" t="n">
-        <v>2651</v>
+        <v>19303</v>
       </c>
       <c r="E23" s="16" t="n">
-        <v>2062</v>
+        <v>15662</v>
       </c>
       <c r="F23" s="16" t="n">
-        <v>1549</v>
+        <v>17964</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>Udskudt skatteaktiv</t>
+          <t>Værdipapirer</t>
         </is>
       </c>
       <c r="B24" s="16" t="n"/>
-      <c r="C24" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" s="16" t="n">
-        <v>3048</v>
-      </c>
-      <c r="E24" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" s="16" t="n">
-        <v>0</v>
-      </c>
+      <c r="C24" s="16" t="n"/>
+      <c r="D24" s="16" t="n"/>
+      <c r="E24" s="16" t="n"/>
+      <c r="F24" s="16" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>Tilgodehavende skat hos tilknyttede virksomheder</t>
-        </is>
-      </c>
-      <c r="B25" s="16" t="n"/>
-      <c r="C25" s="16" t="n"/>
-      <c r="D25" s="16" t="n"/>
-      <c r="E25" s="16" t="n"/>
-      <c r="F25" s="16" t="n"/>
+          <t>Likvide beholdninger</t>
+        </is>
+      </c>
+      <c r="B25" s="16" t="n">
+        <v>1582</v>
+      </c>
+      <c r="C25" s="16" t="n">
+        <v>1381</v>
+      </c>
+      <c r="D25" s="16" t="n">
+        <v>1539</v>
+      </c>
+      <c r="E25" s="16" t="n">
+        <v>1639</v>
+      </c>
+      <c r="F25" s="16" t="n">
+        <v>5121</v>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="15" t="inlineStr">
-        <is>
-          <t>Kortfristede skattetilgodehavender</t>
+      <c r="A26" s="17" t="inlineStr">
+        <is>
+          <t>Omsætningsaktiver</t>
         </is>
       </c>
       <c r="B26" s="16" t="n">
-        <v>5</v>
+        <v>64887</v>
       </c>
       <c r="C26" s="16" t="n">
-        <v>11</v>
+        <v>80434</v>
       </c>
       <c r="D26" s="16" t="n">
-        <v>10</v>
+        <v>60945</v>
       </c>
       <c r="E26" s="16" t="n">
-        <v>2</v>
+        <v>41547</v>
       </c>
       <c r="F26" s="16" t="n">
-        <v>5</v>
+        <v>42398</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="17" t="inlineStr">
         <is>
-          <t>Tilgodehavender</t>
+          <t>Aktiver</t>
         </is>
       </c>
       <c r="B27" s="16" t="n">
-        <v>27501</v>
+        <v>184868</v>
       </c>
       <c r="C27" s="16" t="n">
-        <v>22909</v>
+        <v>209264</v>
       </c>
       <c r="D27" s="16" t="n">
-        <v>30748</v>
+        <v>190659</v>
       </c>
       <c r="E27" s="16" t="n">
-        <v>19303</v>
+        <v>178412</v>
       </c>
       <c r="F27" s="16" t="n">
-        <v>15662</v>
+        <v>168272</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="15" t="inlineStr">
         <is>
-          <t>Værdipapirer</t>
-        </is>
-      </c>
-      <c r="B28" s="16" t="n"/>
-      <c r="C28" s="16" t="n"/>
-      <c r="D28" s="16" t="n"/>
-      <c r="E28" s="16" t="n"/>
-      <c r="F28" s="16" t="n"/>
+          <t>Selskabskapital</t>
+        </is>
+      </c>
+      <c r="B28" s="16" t="n">
+        <v>5760</v>
+      </c>
+      <c r="C28" s="16" t="n">
+        <v>5760</v>
+      </c>
+      <c r="D28" s="16" t="n">
+        <v>6000</v>
+      </c>
+      <c r="E28" s="16" t="n">
+        <v>6000</v>
+      </c>
+      <c r="F28" s="16" t="n">
+        <v>6000</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="15" t="inlineStr">
         <is>
-          <t>Likvide beholdninger</t>
+          <t>Reserve for nettoopskrivning (indre værdis metode)</t>
         </is>
       </c>
       <c r="B29" s="16" t="n">
-        <v>1355</v>
+        <v>423</v>
       </c>
       <c r="C29" s="16" t="n">
-        <v>1582</v>
+        <v>464</v>
       </c>
       <c r="D29" s="16" t="n">
-        <v>1381</v>
+        <v>647</v>
       </c>
       <c r="E29" s="16" t="n">
-        <v>1539</v>
-      </c>
-      <c r="F29" s="16" t="n">
-        <v>1639</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F29" s="16" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="17" t="inlineStr">
-        <is>
-          <t>Omsætningsaktiver</t>
-        </is>
-      </c>
-      <c r="B30" s="16" t="n">
-        <v>63327</v>
-      </c>
-      <c r="C30" s="16" t="n">
-        <v>64887</v>
-      </c>
-      <c r="D30" s="16" t="n">
-        <v>80434</v>
-      </c>
-      <c r="E30" s="16" t="n">
-        <v>60945</v>
-      </c>
-      <c r="F30" s="16" t="n">
-        <v>41547</v>
-      </c>
+      <c r="A30" s="15" t="inlineStr">
+        <is>
+          <t>Reserve for udviklingsomkostninger</t>
+        </is>
+      </c>
+      <c r="B30" s="16" t="n"/>
+      <c r="C30" s="16" t="n"/>
+      <c r="D30" s="16" t="n"/>
+      <c r="E30" s="16" t="n"/>
+      <c r="F30" s="16" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="17" t="inlineStr">
-        <is>
-          <t>Aktiver</t>
-        </is>
-      </c>
-      <c r="B31" s="16" t="n">
-        <v>189294</v>
-      </c>
-      <c r="C31" s="16" t="n">
-        <v>184868</v>
-      </c>
-      <c r="D31" s="16" t="n">
-        <v>209264</v>
-      </c>
-      <c r="E31" s="16" t="n">
-        <v>190659</v>
-      </c>
-      <c r="F31" s="16" t="n">
-        <v>178412</v>
-      </c>
+      <c r="A31" s="15" t="inlineStr">
+        <is>
+          <t>Reserve for sikringstransaktioner</t>
+        </is>
+      </c>
+      <c r="B31" s="16" t="n"/>
+      <c r="C31" s="16" t="n"/>
+      <c r="D31" s="16" t="n"/>
+      <c r="E31" s="16" t="n"/>
+      <c r="F31" s="16" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>Selskabskapital</t>
+          <t>Andre reserver</t>
         </is>
       </c>
       <c r="B32" s="16" t="n">
-        <v>5760</v>
+        <v>1218</v>
       </c>
       <c r="C32" s="16" t="n">
-        <v>5760</v>
+        <v>1218</v>
       </c>
       <c r="D32" s="16" t="n">
-        <v>5760</v>
+        <v>1218</v>
       </c>
       <c r="E32" s="16" t="n">
-        <v>6000</v>
+        <v>1218</v>
       </c>
       <c r="F32" s="16" t="n">
-        <v>6000</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="15" t="inlineStr">
         <is>
-          <t>Reserve for nettoopskrivning (indre værdis metode)</t>
+          <t>Overført resultat</t>
         </is>
       </c>
       <c r="B33" s="16" t="n">
-        <v>470</v>
+        <v>44123</v>
       </c>
       <c r="C33" s="16" t="n">
-        <v>423</v>
+        <v>11623</v>
       </c>
       <c r="D33" s="16" t="n">
-        <v>464</v>
+        <v>8679</v>
       </c>
       <c r="E33" s="16" t="n">
-        <v>647</v>
+        <v>31433</v>
       </c>
       <c r="F33" s="16" t="n">
-        <v>0</v>
+        <v>35107</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="15" t="inlineStr">
-        <is>
-          <t>Reserve for udviklingsomkostninger</t>
-        </is>
-      </c>
-      <c r="B34" s="16" t="n"/>
-      <c r="C34" s="16" t="n"/>
-      <c r="D34" s="16" t="n"/>
-      <c r="E34" s="16" t="n"/>
-      <c r="F34" s="16" t="n"/>
+      <c r="A34" s="17" t="inlineStr">
+        <is>
+          <t>Egenkapital i alt</t>
+        </is>
+      </c>
+      <c r="B34" s="16" t="n">
+        <v>51524</v>
+      </c>
+      <c r="C34" s="16" t="n">
+        <v>19065</v>
+      </c>
+      <c r="D34" s="16" t="n">
+        <v>16544</v>
+      </c>
+      <c r="E34" s="16" t="n">
+        <v>38651</v>
+      </c>
+      <c r="F34" s="16" t="n">
+        <v>42325</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="15" t="inlineStr">
         <is>
-          <t>Reserve for sikringstransaktioner</t>
-        </is>
-      </c>
-      <c r="B35" s="16" t="n"/>
-      <c r="C35" s="16" t="n"/>
+          <t>Hensættelse til udskudt skat</t>
+        </is>
+      </c>
+      <c r="B35" s="16" t="n">
+        <v>6061</v>
+      </c>
+      <c r="C35" s="16" t="n">
+        <v>0</v>
+      </c>
       <c r="D35" s="16" t="n"/>
       <c r="E35" s="16" t="n"/>
       <c r="F35" s="16" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="15" t="inlineStr">
-        <is>
-          <t>Andre reserver</t>
+      <c r="A36" s="17" t="inlineStr">
+        <is>
+          <t>Hensatte forpligtelser</t>
         </is>
       </c>
       <c r="B36" s="16" t="n">
-        <v>1218</v>
+        <v>6061</v>
       </c>
       <c r="C36" s="16" t="n">
-        <v>1218</v>
+        <v>0</v>
       </c>
       <c r="D36" s="16" t="n">
-        <v>1218</v>
+        <v>4610</v>
       </c>
       <c r="E36" s="16" t="n">
-        <v>1218</v>
+        <v>4810</v>
       </c>
       <c r="F36" s="16" t="n">
-        <v>1218</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="15" t="inlineStr">
         <is>
-          <t>Overført resultat</t>
-        </is>
-      </c>
-      <c r="B37" s="16" t="n">
-        <v>57408</v>
-      </c>
-      <c r="C37" s="16" t="n">
-        <v>44123</v>
-      </c>
-      <c r="D37" s="16" t="n">
-        <v>11623</v>
-      </c>
-      <c r="E37" s="16" t="n">
-        <v>8679</v>
-      </c>
-      <c r="F37" s="16" t="n">
-        <v>31433</v>
-      </c>
+          <t>Ansvarlig lånekapital (langfristet)</t>
+        </is>
+      </c>
+      <c r="B37" s="16" t="n"/>
+      <c r="C37" s="16" t="n"/>
+      <c r="D37" s="16" t="n"/>
+      <c r="E37" s="16" t="n"/>
+      <c r="F37" s="16" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="17" t="inlineStr">
-        <is>
-          <t>Egenkapital i alt</t>
-        </is>
-      </c>
-      <c r="B38" s="16" t="n">
-        <v>64589</v>
-      </c>
-      <c r="C38" s="16" t="n">
-        <v>51524</v>
-      </c>
-      <c r="D38" s="16" t="n">
-        <v>19065</v>
-      </c>
-      <c r="E38" s="16" t="n">
-        <v>16544</v>
-      </c>
-      <c r="F38" s="16" t="n">
-        <v>38651</v>
-      </c>
+      <c r="A38" s="15" t="inlineStr">
+        <is>
+          <t>Langfristede lån</t>
+        </is>
+      </c>
+      <c r="B38" s="16" t="n"/>
+      <c r="C38" s="16" t="n"/>
+      <c r="D38" s="16" t="n"/>
+      <c r="E38" s="16" t="n"/>
+      <c r="F38" s="16" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="15" t="inlineStr">
         <is>
-          <t>Hensættelse til udskudt skat</t>
-        </is>
-      </c>
-      <c r="B39" s="16" t="n">
-        <v>9626</v>
-      </c>
-      <c r="C39" s="16" t="n">
-        <v>6061</v>
-      </c>
-      <c r="D39" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E39" s="16" t="n"/>
-      <c r="F39" s="16" t="n"/>
+          <t>Leasingforpligtelser (langfristet)</t>
+        </is>
+      </c>
+      <c r="B39" s="16" t="n"/>
+      <c r="C39" s="16" t="n"/>
+      <c r="D39" s="16" t="n"/>
+      <c r="E39" s="16" t="n">
+        <v>925</v>
+      </c>
+      <c r="F39" s="16" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" s="17" t="inlineStr">
-        <is>
-          <t>Hensatte forpligtelser</t>
-        </is>
-      </c>
-      <c r="B40" s="16" t="n">
-        <v>9626</v>
-      </c>
-      <c r="C40" s="16" t="n">
-        <v>6061</v>
-      </c>
-      <c r="D40" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E40" s="16" t="n">
-        <v>4610</v>
-      </c>
-      <c r="F40" s="16" t="n">
-        <v>4810</v>
-      </c>
+      <c r="A40" s="15" t="inlineStr">
+        <is>
+          <t>Anden gæld (langfristet)</t>
+        </is>
+      </c>
+      <c r="B40" s="16" t="n"/>
+      <c r="C40" s="16" t="n"/>
+      <c r="D40" s="16" t="n"/>
+      <c r="E40" s="16" t="n"/>
+      <c r="F40" s="16" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="15" t="inlineStr">
-        <is>
-          <t>Ansvarlig lånekapital (langfristet)</t>
-        </is>
-      </c>
-      <c r="B41" s="16" t="n"/>
-      <c r="C41" s="16" t="n"/>
-      <c r="D41" s="16" t="n"/>
-      <c r="E41" s="16" t="n"/>
-      <c r="F41" s="16" t="n"/>
+      <c r="A41" s="17" t="inlineStr">
+        <is>
+          <t>Langfristede gældsforpligtelser</t>
+        </is>
+      </c>
+      <c r="B41" s="16" t="n">
+        <v>4775</v>
+      </c>
+      <c r="C41" s="16" t="n">
+        <v>3731</v>
+      </c>
+      <c r="D41" s="16" t="n">
+        <v>3720</v>
+      </c>
+      <c r="E41" s="16" t="n">
+        <v>5098</v>
+      </c>
+      <c r="F41" s="16" t="n">
+        <v>5018</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="15" t="inlineStr">
         <is>
-          <t>Langfristede lån</t>
-        </is>
-      </c>
-      <c r="B42" s="16" t="n">
-        <v>26396</v>
-      </c>
+          <t>Ansvarlig lånekapital (kortfristet)</t>
+        </is>
+      </c>
+      <c r="B42" s="16" t="n"/>
       <c r="C42" s="16" t="n"/>
       <c r="D42" s="16" t="n"/>
       <c r="E42" s="16" t="n"/>
@@ -5919,163 +5736,159 @@
     <row r="43">
       <c r="A43" s="15" t="inlineStr">
         <is>
-          <t>Leasingforpligtelser (langfristet)</t>
-        </is>
-      </c>
-      <c r="B43" s="16" t="n">
-        <v>12059</v>
-      </c>
+          <t>Kortfristet del af langfristede gældsforpligtelser</t>
+        </is>
+      </c>
+      <c r="B43" s="16" t="n"/>
       <c r="C43" s="16" t="n"/>
       <c r="D43" s="16" t="n"/>
       <c r="E43" s="16" t="n"/>
-      <c r="F43" s="16" t="n">
-        <v>925</v>
-      </c>
+      <c r="F43" s="16" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="15" t="inlineStr">
         <is>
-          <t>Anden gæld (langfristet)</t>
-        </is>
-      </c>
-      <c r="B44" s="16" t="n"/>
-      <c r="C44" s="16" t="n"/>
-      <c r="D44" s="16" t="n"/>
-      <c r="E44" s="16" t="n"/>
-      <c r="F44" s="16" t="n"/>
+          <t>Kreditinstitutter</t>
+        </is>
+      </c>
+      <c r="B44" s="16" t="n">
+        <v>11210</v>
+      </c>
+      <c r="C44" s="16" t="n">
+        <v>4978</v>
+      </c>
+      <c r="D44" s="16" t="n">
+        <v>9908</v>
+      </c>
+      <c r="E44" s="16" t="n">
+        <v>9186</v>
+      </c>
+      <c r="F44" s="16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" s="17" t="inlineStr">
-        <is>
-          <t>Langfristede gældsforpligtelser</t>
-        </is>
-      </c>
-      <c r="B45" s="16" t="n">
-        <v>42255</v>
-      </c>
-      <c r="C45" s="16" t="n">
-        <v>4775</v>
-      </c>
-      <c r="D45" s="16" t="n">
-        <v>3731</v>
-      </c>
+      <c r="A45" s="15" t="inlineStr">
+        <is>
+          <t>Leasingforpligtelser (kortfristet)</t>
+        </is>
+      </c>
+      <c r="B45" s="16" t="n"/>
+      <c r="C45" s="16" t="n"/>
+      <c r="D45" s="16" t="n"/>
       <c r="E45" s="16" t="n">
-        <v>3720</v>
+        <v>1055</v>
       </c>
       <c r="F45" s="16" t="n">
-        <v>5098</v>
+        <v>906</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="15" t="inlineStr">
         <is>
-          <t>Ansvarlig lånekapital (kortfristet)</t>
-        </is>
-      </c>
-      <c r="B46" s="16" t="n"/>
-      <c r="C46" s="16" t="n"/>
-      <c r="D46" s="16" t="n"/>
-      <c r="E46" s="16" t="n"/>
-      <c r="F46" s="16" t="n"/>
+          <t>Leverandører af varer og tjenesteydelser</t>
+        </is>
+      </c>
+      <c r="B46" s="16" t="n">
+        <v>12863</v>
+      </c>
+      <c r="C46" s="16" t="n">
+        <v>19864</v>
+      </c>
+      <c r="D46" s="16" t="n">
+        <v>18659</v>
+      </c>
+      <c r="E46" s="16" t="n">
+        <v>27960</v>
+      </c>
+      <c r="F46" s="16" t="n">
+        <v>5732</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="15" t="inlineStr">
         <is>
-          <t>Kortfristet del af langfristede gældsforpligtelser</t>
+          <t>Gæld til tilknyttede virksomheder</t>
         </is>
       </c>
       <c r="B47" s="16" t="n">
-        <v>3049</v>
-      </c>
-      <c r="C47" s="16" t="n"/>
-      <c r="D47" s="16" t="n"/>
-      <c r="E47" s="16" t="n"/>
-      <c r="F47" s="16" t="n"/>
+        <v>77617</v>
+      </c>
+      <c r="C47" s="16" t="n">
+        <v>142638</v>
+      </c>
+      <c r="D47" s="16" t="n">
+        <v>115904</v>
+      </c>
+      <c r="E47" s="16" t="n">
+        <v>84110</v>
+      </c>
+      <c r="F47" s="16" t="n">
+        <v>103465</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="15" t="inlineStr">
         <is>
-          <t>Kreditinstitutter</t>
-        </is>
-      </c>
-      <c r="B48" s="16" t="n">
-        <v>27753</v>
-      </c>
-      <c r="C48" s="16" t="n">
-        <v>11210</v>
-      </c>
-      <c r="D48" s="16" t="n">
-        <v>4978</v>
-      </c>
-      <c r="E48" s="16" t="n">
-        <v>9908</v>
-      </c>
-      <c r="F48" s="16" t="n">
-        <v>9186</v>
-      </c>
+          <t>Gæld til selskabsdeltagere og ledelse</t>
+        </is>
+      </c>
+      <c r="B48" s="16" t="n"/>
+      <c r="C48" s="16" t="n"/>
+      <c r="D48" s="16" t="n"/>
+      <c r="E48" s="16" t="n"/>
+      <c r="F48" s="16" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="15" t="inlineStr">
         <is>
-          <t>Leasingforpligtelser (kortfristet)</t>
+          <t>Selskabsskat</t>
         </is>
       </c>
       <c r="B49" s="16" t="n"/>
       <c r="C49" s="16" t="n"/>
       <c r="D49" s="16" t="n"/>
       <c r="E49" s="16" t="n"/>
-      <c r="F49" s="16" t="n">
-        <v>1055</v>
-      </c>
+      <c r="F49" s="16" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="15" t="inlineStr">
         <is>
-          <t>Leverandører af varer og tjenesteydelser</t>
-        </is>
-      </c>
-      <c r="B50" s="16" t="n">
-        <v>18502</v>
-      </c>
-      <c r="C50" s="16" t="n">
-        <v>12863</v>
-      </c>
-      <c r="D50" s="16" t="n">
-        <v>19864</v>
-      </c>
-      <c r="E50" s="16" t="n">
-        <v>18659</v>
-      </c>
-      <c r="F50" s="16" t="n">
-        <v>27960</v>
-      </c>
+          <t>Gæld til tilknyttede virksomheder vedr. selskabsskat</t>
+        </is>
+      </c>
+      <c r="B50" s="16" t="n"/>
+      <c r="C50" s="16" t="n"/>
+      <c r="D50" s="16" t="n"/>
+      <c r="E50" s="16" t="n"/>
+      <c r="F50" s="16" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="15" t="inlineStr">
         <is>
-          <t>Gæld til tilknyttede virksomheder</t>
+          <t>Anden gæld (kortfristet)</t>
         </is>
       </c>
       <c r="B51" s="16" t="n">
-        <v>3665</v>
+        <v>20818</v>
       </c>
       <c r="C51" s="16" t="n">
-        <v>77617</v>
+        <v>18989</v>
       </c>
       <c r="D51" s="16" t="n">
-        <v>142638</v>
+        <v>21314</v>
       </c>
       <c r="E51" s="16" t="n">
-        <v>115904</v>
+        <v>7541</v>
       </c>
       <c r="F51" s="16" t="n">
-        <v>84110</v>
+        <v>10827</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="15" t="inlineStr">
         <is>
-          <t>Gæld til selskabsdeltagere og ledelse</t>
+          <t>Periodeafgrænsningsposter (passiver)</t>
         </is>
       </c>
       <c r="B52" s="16" t="n"/>
@@ -6085,127 +5898,69 @@
       <c r="F52" s="16" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="15" t="inlineStr">
-        <is>
-          <t>Selskabsskat</t>
-        </is>
-      </c>
-      <c r="B53" s="16" t="n"/>
-      <c r="C53" s="16" t="n"/>
-      <c r="D53" s="16" t="n"/>
-      <c r="E53" s="16" t="n"/>
-      <c r="F53" s="16" t="n"/>
+      <c r="A53" s="17" t="inlineStr">
+        <is>
+          <t>Kortfristede gældsforpligtelser</t>
+        </is>
+      </c>
+      <c r="B53" s="16" t="n">
+        <v>122508</v>
+      </c>
+      <c r="C53" s="16" t="n">
+        <v>186469</v>
+      </c>
+      <c r="D53" s="16" t="n">
+        <v>165785</v>
+      </c>
+      <c r="E53" s="16" t="n">
+        <v>129853</v>
+      </c>
+      <c r="F53" s="16" t="n">
+        <v>120930</v>
+      </c>
     </row>
     <row r="54">
-      <c r="A54" s="15" t="inlineStr">
-        <is>
-          <t>Gæld til tilknyttede virksomheder vedr. selskabsskat</t>
-        </is>
-      </c>
-      <c r="B54" s="16" t="n"/>
-      <c r="C54" s="16" t="n"/>
-      <c r="D54" s="16" t="n"/>
-      <c r="E54" s="16" t="n"/>
-      <c r="F54" s="16" t="n"/>
+      <c r="A54" s="17" t="inlineStr">
+        <is>
+          <t>Gældsforpligtelser</t>
+        </is>
+      </c>
+      <c r="B54" s="16" t="n">
+        <v>127283</v>
+      </c>
+      <c r="C54" s="16" t="n">
+        <v>190200</v>
+      </c>
+      <c r="D54" s="16" t="n">
+        <v>169505</v>
+      </c>
+      <c r="E54" s="16" t="n">
+        <v>134951</v>
+      </c>
+      <c r="F54" s="16" t="n">
+        <v>125948</v>
+      </c>
     </row>
     <row r="55">
-      <c r="A55" s="15" t="inlineStr">
-        <is>
-          <t>Anden gæld (kortfristet)</t>
+      <c r="A55" s="17" t="inlineStr">
+        <is>
+          <t>Passiver</t>
         </is>
       </c>
       <c r="B55" s="16" t="n">
-        <v>23520</v>
+        <v>184868</v>
       </c>
       <c r="C55" s="16" t="n">
-        <v>20818</v>
+        <v>209264</v>
       </c>
       <c r="D55" s="16" t="n">
-        <v>18989</v>
+        <v>190659</v>
       </c>
       <c r="E55" s="16" t="n">
-        <v>21314</v>
+        <v>178412</v>
       </c>
       <c r="F55" s="16" t="n">
-        <v>7541</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="15" t="inlineStr">
-        <is>
-          <t>Periodeafgrænsningsposter (passiver)</t>
-        </is>
-      </c>
-      <c r="B56" s="16" t="n"/>
-      <c r="C56" s="16" t="n"/>
-      <c r="D56" s="16" t="n"/>
-      <c r="E56" s="16" t="n"/>
-      <c r="F56" s="16" t="n"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="17" t="inlineStr">
-        <is>
-          <t>Kortfristede gældsforpligtelser</t>
-        </is>
-      </c>
-      <c r="B57" s="16" t="n">
-        <v>72824</v>
-      </c>
-      <c r="C57" s="16" t="n">
-        <v>122508</v>
-      </c>
-      <c r="D57" s="16" t="n">
-        <v>186469</v>
-      </c>
-      <c r="E57" s="16" t="n">
-        <v>165785</v>
-      </c>
-      <c r="F57" s="16" t="n">
-        <v>129853</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="17" t="inlineStr">
-        <is>
-          <t>Gældsforpligtelser</t>
-        </is>
-      </c>
-      <c r="B58" s="16" t="n">
-        <v>115079</v>
-      </c>
-      <c r="C58" s="16" t="n">
-        <v>127283</v>
-      </c>
-      <c r="D58" s="16" t="n">
-        <v>190200</v>
-      </c>
-      <c r="E58" s="16" t="n">
-        <v>169505</v>
-      </c>
-      <c r="F58" s="16" t="n">
-        <v>134951</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="17" t="inlineStr">
-        <is>
-          <t>Passiver</t>
-        </is>
-      </c>
-      <c r="B59" s="16" t="n">
-        <v>189294</v>
-      </c>
-      <c r="C59" s="16" t="n">
-        <v>184868</v>
-      </c>
-      <c r="D59" s="16" t="n">
-        <v>209264</v>
-      </c>
-      <c r="E59" s="16" t="n">
-        <v>190659</v>
-      </c>
-      <c r="F59" s="16" t="n">
-        <v>178412</v>
+        <v>168272</v>
       </c>
     </row>
   </sheetData>
@@ -6244,13 +5999,13 @@
         </is>
       </c>
       <c r="B3" s="20" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C3" s="20" t="n">
         <v>2024</v>
       </c>
-      <c r="C3" s="20" t="n">
+      <c r="D3" s="20" t="n">
         <v>2023</v>
-      </c>
-      <c r="D3" s="20" t="n">
-        <v>2022</v>
       </c>
       <c r="F3" s="21" t="inlineStr">
         <is>
@@ -6558,15 +6313,15 @@
         </is>
       </c>
       <c r="B18" s="24">
-        <f>'balance_raw_37118311'!$F$15</f>
+        <f>'balance_raw_37118311'!$F$11</f>
         <v/>
       </c>
       <c r="C18" s="24">
-        <f>'balance_raw_37118311'!$E$15</f>
+        <f>'balance_raw_37118311'!$E$11</f>
         <v/>
       </c>
       <c r="D18" s="24">
-        <f>'balance_raw_37118311'!$D$15</f>
+        <f>'balance_raw_37118311'!$D$11</f>
         <v/>
       </c>
       <c r="F18" s="25" t="inlineStr">
@@ -6582,15 +6337,15 @@
         </is>
       </c>
       <c r="B19" s="24">
-        <f>'balance_raw_37118311'!$F$30</f>
+        <f>'balance_raw_37118311'!$F$26</f>
         <v/>
       </c>
       <c r="C19" s="24">
-        <f>'balance_raw_37118311'!$E$30</f>
+        <f>'balance_raw_37118311'!$E$26</f>
         <v/>
       </c>
       <c r="D19" s="24">
-        <f>'balance_raw_37118311'!$D$30</f>
+        <f>'balance_raw_37118311'!$D$26</f>
         <v/>
       </c>
       <c r="F19" s="25" t="inlineStr">
@@ -6637,15 +6392,15 @@
         </is>
       </c>
       <c r="B22" s="24">
-        <f>'balance_raw_37118311'!$F$38</f>
+        <f>'balance_raw_37118311'!$F$34</f>
         <v/>
       </c>
       <c r="C22" s="24">
-        <f>'balance_raw_37118311'!$E$38</f>
+        <f>'balance_raw_37118311'!$E$34</f>
         <v/>
       </c>
       <c r="D22" s="24">
-        <f>'balance_raw_37118311'!$D$38</f>
+        <f>'balance_raw_37118311'!$D$34</f>
         <v/>
       </c>
       <c r="F22" s="25" t="inlineStr">
@@ -6661,15 +6416,15 @@
         </is>
       </c>
       <c r="B23" s="24">
-        <f>'balance_raw_37118311'!$F$59-'balance_raw_37118311'!$F$38</f>
+        <f>'balance_raw_37118311'!$F$55-'balance_raw_37118311'!$F$34</f>
         <v/>
       </c>
       <c r="C23" s="24">
-        <f>'balance_raw_37118311'!$E$59-'balance_raw_37118311'!$E$38</f>
+        <f>'balance_raw_37118311'!$E$55-'balance_raw_37118311'!$E$34</f>
         <v/>
       </c>
       <c r="D23" s="24">
-        <f>'balance_raw_37118311'!$D$59-'balance_raw_37118311'!$D$38</f>
+        <f>'balance_raw_37118311'!$D$55-'balance_raw_37118311'!$D$34</f>
         <v/>
       </c>
       <c r="F23" s="25" t="inlineStr">
@@ -6727,15 +6482,15 @@
         </is>
       </c>
       <c r="B27" s="24">
-        <f>'balance_raw_37118311'!$F$19</f>
+        <f>'balance_raw_37118311'!$F$15</f>
         <v/>
       </c>
       <c r="C27" s="24">
-        <f>'balance_raw_37118311'!$E$19</f>
+        <f>'balance_raw_37118311'!$E$15</f>
         <v/>
       </c>
       <c r="D27" s="24">
-        <f>'balance_raw_37118311'!$D$19</f>
+        <f>'balance_raw_37118311'!$D$15</f>
         <v/>
       </c>
       <c r="F27" s="25" t="inlineStr">
@@ -6751,15 +6506,15 @@
         </is>
       </c>
       <c r="B28" s="24">
-        <f>'balance_raw_37118311'!$F$20</f>
+        <f>'balance_raw_37118311'!$F$16</f>
         <v/>
       </c>
       <c r="C28" s="24">
-        <f>'balance_raw_37118311'!$E$20</f>
+        <f>'balance_raw_37118311'!$E$16</f>
         <v/>
       </c>
       <c r="D28" s="24">
-        <f>'balance_raw_37118311'!$D$20</f>
+        <f>'balance_raw_37118311'!$D$16</f>
         <v/>
       </c>
       <c r="F28" s="25" t="inlineStr">
@@ -6775,15 +6530,15 @@
         </is>
       </c>
       <c r="B29" s="24">
-        <f>'balance_raw_37118311'!$F$57</f>
+        <f>'balance_raw_37118311'!$F$53</f>
         <v/>
       </c>
       <c r="C29" s="24">
-        <f>'balance_raw_37118311'!$E$57</f>
+        <f>'balance_raw_37118311'!$E$53</f>
         <v/>
       </c>
       <c r="D29" s="24">
-        <f>'balance_raw_37118311'!$D$57</f>
+        <f>'balance_raw_37118311'!$D$53</f>
         <v/>
       </c>
       <c r="F29" s="25" t="inlineStr">
@@ -6940,7 +6695,7 @@
     <row r="39">
       <c r="A39" s="22" t="inlineStr">
         <is>
-          <t>Indekstal for indtjeningsevne (2022=100)</t>
+          <t>Indekstal for indtjeningsevne (2023=100)</t>
         </is>
       </c>
       <c r="B39" s="22" t="n"/>
@@ -7058,7 +6813,7 @@
     <row r="46">
       <c r="A46" s="22" t="inlineStr">
         <is>
-          <t>Indekstal for kapitaltilpasningsevne (2022=100)</t>
+          <t>Indekstal for kapitaltilpasningsevne (2023=100)</t>
         </is>
       </c>
       <c r="B46" s="22" t="n"/>
@@ -7234,7 +6989,7 @@
     <row r="57">
       <c r="A57" s="32" t="inlineStr">
         <is>
-          <t>Kilde: Bearbejdet uddrag af årsrapporter for 2022-2024. Alle dataceller er live formler der peger på res_raw / balance_raw.</t>
+          <t>Kilde: Bearbejdet uddrag af årsrapporter for 2023-2025. Alle dataceller er live formler der peger på res_raw / balance_raw.</t>
         </is>
       </c>
       <c r="B57" s="29" t="n"/>
@@ -7267,15 +7022,15 @@
         </is>
       </c>
       <c r="B60" s="29">
-        <f>IF('balance_raw_37118311'!$F$31="","—",IF(ABS(B20-'balance_raw_37118311'!$F$31)&lt;=1,"✓ OK","❌ "&amp;TEXT(B20-'balance_raw_37118311'!$F$31,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('balance_raw_37118311'!$F$27="","—",IF(ABS(B20-'balance_raw_37118311'!$F$27)&lt;=1,"✓ OK","❌ "&amp;TEXT(B20-'balance_raw_37118311'!$F$27,"+#,##0;-#,##0")&amp;" t.kr."))</f>
         <v/>
       </c>
       <c r="C60" s="29">
-        <f>IF('balance_raw_37118311'!$E$31="","—",IF(ABS(C20-'balance_raw_37118311'!$E$31)&lt;=1,"✓ OK","❌ "&amp;TEXT(C20-'balance_raw_37118311'!$E$31,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('balance_raw_37118311'!$E$27="","—",IF(ABS(C20-'balance_raw_37118311'!$E$27)&lt;=1,"✓ OK","❌ "&amp;TEXT(C20-'balance_raw_37118311'!$E$27,"+#,##0;-#,##0")&amp;" t.kr."))</f>
         <v/>
       </c>
       <c r="D60" s="29">
-        <f>IF('balance_raw_37118311'!$D$31="","—",IF(ABS(D20-'balance_raw_37118311'!$D$31)&lt;=1,"✓ OK","❌ "&amp;TEXT(D20-'balance_raw_37118311'!$D$31,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('balance_raw_37118311'!$D$27="","—",IF(ABS(D20-'balance_raw_37118311'!$D$27)&lt;=1,"✓ OK","❌ "&amp;TEXT(D20-'balance_raw_37118311'!$D$27,"+#,##0;-#,##0")&amp;" t.kr."))</f>
         <v/>
       </c>
       <c r="F60" s="25" t="inlineStr">
@@ -7291,15 +7046,15 @@
         </is>
       </c>
       <c r="B61" s="29">
-        <f>IF('balance_raw_37118311'!$F$59="","—",IF(ABS(B24-'balance_raw_37118311'!$F$59)&lt;=1,"✓ OK","❌ "&amp;TEXT(B24-'balance_raw_37118311'!$F$59,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('balance_raw_37118311'!$F$55="","—",IF(ABS(B24-'balance_raw_37118311'!$F$55)&lt;=1,"✓ OK","❌ "&amp;TEXT(B24-'balance_raw_37118311'!$F$55,"+#,##0;-#,##0")&amp;" t.kr."))</f>
         <v/>
       </c>
       <c r="C61" s="29">
-        <f>IF('balance_raw_37118311'!$E$59="","—",IF(ABS(C24-'balance_raw_37118311'!$E$59)&lt;=1,"✓ OK","❌ "&amp;TEXT(C24-'balance_raw_37118311'!$E$59,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('balance_raw_37118311'!$E$55="","—",IF(ABS(C24-'balance_raw_37118311'!$E$55)&lt;=1,"✓ OK","❌ "&amp;TEXT(C24-'balance_raw_37118311'!$E$55,"+#,##0;-#,##0")&amp;" t.kr."))</f>
         <v/>
       </c>
       <c r="D61" s="29">
-        <f>IF('balance_raw_37118311'!$D$59="","—",IF(ABS(D24-'balance_raw_37118311'!$D$59)&lt;=1,"✓ OK","❌ "&amp;TEXT(D24-'balance_raw_37118311'!$D$59,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('balance_raw_37118311'!$D$55="","—",IF(ABS(D24-'balance_raw_37118311'!$D$55)&lt;=1,"✓ OK","❌ "&amp;TEXT(D24-'balance_raw_37118311'!$D$55,"+#,##0;-#,##0")&amp;" t.kr."))</f>
         <v/>
       </c>
       <c r="F61" s="25" t="inlineStr">
